--- a/docs/GameBalance.updated.xlsx
+++ b/docs/GameBalance.updated.xlsx
@@ -1,27 +1,27 @@
 
-<file path=xl\featurePropertyBag\featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <xfpb:bag type="Checkbox"/>
-  <xfpb:bag type="XFControls">
-    <xfpb:bagId k="CellControl">0</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplement">
-    <xfpb:bagId k="XFControls">1</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <xfpb:a k="MappedFeaturePropertyBags">
-      <xfpb:bagId>2</xfpb:bagId>
-    </xfpb:a>
-  </xfpb:bag>
-</xfpb:FeaturePropertyBags>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Artifacts" sheetId="1" r:id="Rd9a3327a4bbb4e20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synergies" sheetId="2" r:id="R0495bcc079054396"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="3" r:id="R34a753bc4d2445dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Waves" sheetId="4" r:id="R7df57794d53040c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Playtest" sheetId="5" r:id="Rd90ac3814c684e51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DamageSystem" sheetId="6" r:id="R1eac87708b694b6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EconomySystem" sheetId="7" r:id="R7a93ce70d2124b06"/>
+  </x:sheets>
+</x:workbook>
 </file>
 
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="#,##0.0"/>
+  </x:numFmts>
   <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
@@ -38,7 +38,7 @@
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
-  <x:fills count="14">
+  <x:fills count="15">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -105,8 +105,13 @@
         <x:fgColor rgb="FF1F4E79"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="12">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -136,11 +141,137 @@
         <x:color rgb="FFD9E2F3"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="48">
+  <x:cellXfs count="79">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center"/>
@@ -248,6 +379,81 @@
     <x:xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -323,7 +529,24 @@
 </x:styleSheet>
 </file>
 
-<file path=xl\tables\table1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ArtifactsBalanceTable" displayName="ArtifactsBalanceTable" ref="A1:CF34" headerRowCount="1">
   <x:tableColumns count="84">
     <x:tableColumn id="1" name="id"/>
@@ -415,7 +638,7 @@
 </x:table>
 </file>
 
-<file path=xl\tables\table2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SynergyBalanceTable" displayName="SynergyBalanceTable" ref="A1:Z36" headerRowCount="1">
   <x:tableColumns count="26">
     <x:tableColumn id="1" name="synergy_type"/>
@@ -449,7 +672,7 @@
 </x:table>
 </file>
 
-<file path=xl\tables\table3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EnemiesBalanceTable" displayName="EnemiesBalanceTable" ref="A1:K5" headerRowCount="1">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="id"/>
@@ -468,7 +691,7 @@
 </x:table>
 </file>
 
-<file path=xl\tables\table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="WaveConfigTable" displayName="WaveConfigTable" ref="A1:J6" headerRowCount="1">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="wave"/>
@@ -486,7 +709,7 @@
 </x:table>
 </file>
 
-<file path=xl\tables\table5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="WaveParameterTable" displayName="WaveParameterTable" ref="A8:C17" headerRowCount="1">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="parameter"/>
@@ -497,7 +720,7 @@
 </x:table>
 </file>
 
-<file path=xl\tables\table6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="DamageArtifactTable" displayName="DamageArtifactTable" ref="A1:S34" headerRowCount="1">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="artifact_id"/>
@@ -524,7 +747,7 @@
 </x:table>
 </file>
 
-<file path=xl\tables\table7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="DamageEnemyTable" displayName="DamageEnemyTable" ref="A36:L40" headerRowCount="1">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="enemy_id"/>
@@ -544,7 +767,7 @@
 </x:table>
 </file>
 
-<file path=xl\tables\table8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="EconomySystemTable" displayName="EconomySystemTable" ref="A1:F45" headerRowCount="1">
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="section"/>
@@ -558,7 +781,7 @@
 </x:table>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -730,43 +953,26 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Artifacts" sheetId="1" r:id="Rf3d315c14016448d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synergies" sheetId="2" r:id="R008a22fc909142fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="3" r:id="R9cae97c625154bcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Waves" sheetId="4" r:id="R83bb0c90dfc541b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Playtest" sheetId="5" r:id="R1ad1b9e72e0243ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DamageSystem" sheetId="6" r:id="R4a0a365e04704eeb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EconomySystem" sheetId="7" r:id="Rb213dd5a8a96496f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Destinies" sheetId="8" r:id="Rdestinies"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Encounters" sheetId="9" r:id="Rencounters"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossWaves" sheetId="10" r:id="Rbosswaves"/>
-  </x:sheets>
-</x:workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18.75" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="17.5" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8.75" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="8.75" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="9.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="11.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="45" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="26.25" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="10.25" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="10.25" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="10.25" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="17.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="6.75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="6.75" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="6.75" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="6.75" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15.25" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="10.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="6.75" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="38.75" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="37.5" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="8.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="8.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="8.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="38.75" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="10.25" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="10.25" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="10.25" hidden="0" customWidth="1"/>
@@ -837,47 +1043,55 @@
     <x:col min="84" max="84" width="22.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="18" customHeight="1">
-      <x:c r="A1" s="47" t="str">
+    <x:row r="1" ht="21" customHeight="1">
+      <x:c r="A1" s="48" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="47" t="str">
+      <x:c r="B1" s="48" t="str">
         <x:v>名称</x:v>
       </x:c>
-      <x:c r="C1" s="47" t="str">
+      <x:c r="C1" s="48" t="str">
         <x:v>类型</x:v>
       </x:c>
-      <x:c r="D1" s="47" t="str">
+      <x:c r="D1" s="48" t="str">
         <x:v>属性</x:v>
       </x:c>
-      <x:c r="E1" s="47" t="str">
+      <x:c r="E1" s="48" t="str">
         <x:v>伤害</x:v>
       </x:c>
-      <x:c r="F1" s="47" t="str">
+      <x:c r="F1" s="48" t="str">
         <x:v>攻速/间隔秒</x:v>
       </x:c>
-      <x:c r="G1" s="47" t="str">
+      <x:c r="G1" s="48" t="str">
         <x:v>范围</x:v>
       </x:c>
-      <x:c r="H1" s="47" t="str">
+      <x:c r="H1" s="48" t="str">
         <x:v>实际价格(灵石)</x:v>
       </x:c>
-      <x:c r="I1" s="47" t="str">
+      <x:c r="I1" s="48" t="str">
         <x:v>费用叫法</x:v>
       </x:c>
-      <x:c r="J1" s="47" t="str">
+      <x:c r="J1" s="48" t="str">
         <x:v>品阶</x:v>
       </x:c>
-      <x:c r="K1" s="47" t="str">
+      <x:c r="K1" s="48" t="str">
         <x:v>效果摘要</x:v>
       </x:c>
-      <x:c r="L1" s="47" t="str">
+      <x:c r="L1" s="48" t="str">
         <x:v>数据来源</x:v>
       </x:c>
-      <x:c r="M1"/>
-      <x:c r="N1"/>
-      <x:c r="O1"/>
-      <x:c r="P1"/>
+      <x:c r="M1" s="48" t="str">
+        <x:v>1星DPS</x:v>
+      </x:c>
+      <x:c r="N1" s="48" t="str">
+        <x:v>2星DPS</x:v>
+      </x:c>
+      <x:c r="O1" s="48" t="str">
+        <x:v>3星DPS</x:v>
+      </x:c>
+      <x:c r="P1" s="48" t="str">
+        <x:v>对群备注</x:v>
+      </x:c>
       <x:c r="Q1"/>
       <x:c r="R1"/>
       <x:c r="S1"/>
@@ -945,45 +1159,55 @@
       <x:c r="CC1"/>
       <x:c r="CD1"/>
     </x:row>
-    <x:row r="2" ht="18" customHeight="1">
-      <x:c r="A2" s="31" t="str">
+    <x:row r="2" ht="34.5" customHeight="1">
+      <x:c r="A2" s="73" t="str">
         <x:v>blood_slash</x:v>
       </x:c>
-      <x:c r="B2" s="31" t="str">
+      <x:c r="B2" s="70" t="str">
         <x:v>血斩</x:v>
       </x:c>
-      <x:c r="C2" s="31" t="str">
+      <x:c r="C2" s="70" t="str">
         <x:v>魔修</x:v>
       </x:c>
-      <x:c r="D2" s="31" t="str">
+      <x:c r="D2" s="70" t="str">
         <x:v>雷</x:v>
       </x:c>
-      <x:c r="E2" s="31" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F2" s="31" t="n">
+      <x:c r="E2" s="74" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F2" s="74" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="G2" s="31" t="n">
+      <x:c r="G2" s="74" t="n">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="H2" s="31" t="n">
+      <x:c r="H2" s="74" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I2" s="31" t="str">
+      <x:c r="I2" s="70" t="str">
         <x:v>2费</x:v>
       </x:c>
-      <x:c r="J2" s="31" t="str">
+      <x:c r="J2" s="70" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="K2" s="31"/>
-      <x:c r="L2" s="31" t="str">
+      <x:c r="K2" s="53" t="str">
+        <x:v>发射宽大的血色剑气。攻击消耗3点生命，生命低于30%时不消耗；击杀敌人回复1点生命。</x:v>
+      </x:c>
+      <x:c r="L2" s="70" t="str">
         <x:v>data/artifacts/blood_slash.tres</x:v>
       </x:c>
-      <x:c r="M2"/>
-      <x:c r="N2"/>
-      <x:c r="O2"/>
-      <x:c r="P2"/>
+      <x:c r="M2" s="74" t="n">
+        <x:v>32.3</x:v>
+      </x:c>
+      <x:c r="N2" s="74" t="n">
+        <x:v>58.9</x:v>
+      </x:c>
+      <x:c r="O2" s="74" t="n">
+        <x:v>103.8</x:v>
+      </x:c>
+      <x:c r="P2" s="64" t="str">
+        <x:v>穿透血色剑气，线形对群中强。</x:v>
+      </x:c>
       <x:c r="Q2"/>
       <x:c r="R2"/>
       <x:c r="S2"/>
@@ -1051,45 +1275,55 @@
       <x:c r="CC2"/>
       <x:c r="CD2"/>
     </x:row>
-    <x:row r="3" ht="18" customHeight="1">
-      <x:c r="A3" s="31" t="str">
+    <x:row r="3" ht="34.5" customHeight="1">
+      <x:c r="A3" s="75" t="str">
         <x:v>blood_sword</x:v>
       </x:c>
-      <x:c r="B3" s="31" t="str">
+      <x:c r="B3" s="71" t="str">
         <x:v>血剑</x:v>
       </x:c>
-      <x:c r="C3" s="31" t="str">
+      <x:c r="C3" s="71" t="str">
         <x:v>魔修</x:v>
       </x:c>
-      <x:c r="D3" s="31" t="str">
+      <x:c r="D3" s="71" t="str">
         <x:v>火</x:v>
       </x:c>
-      <x:c r="E3" s="31" t="n">
+      <x:c r="E3" s="76" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F3" s="31" t="n">
+      <x:c r="F3" s="76" t="n">
         <x:v>0.86</x:v>
       </x:c>
-      <x:c r="G3" s="31" t="n">
+      <x:c r="G3" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H3" s="31" t="n">
+      <x:c r="H3" s="76" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I3" s="31" t="str">
+      <x:c r="I3" s="71" t="str">
         <x:v>1费</x:v>
       </x:c>
-      <x:c r="J3" s="31" t="str">
+      <x:c r="J3" s="71" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="K3" s="31"/>
-      <x:c r="L3" s="31" t="str">
+      <x:c r="K3" s="57" t="str">
+        <x:v>挥出高伤害血色剑光。攻击消耗3点生命，生命低于30%时不消耗；击杀敌人回复1点生命。</x:v>
+      </x:c>
+      <x:c r="L3" s="71" t="str">
         <x:v>data/artifacts/blood_sword.tres</x:v>
       </x:c>
-      <x:c r="M3"/>
-      <x:c r="N3"/>
-      <x:c r="O3"/>
-      <x:c r="P3"/>
+      <x:c r="M3" s="76" t="n">
+        <x:v>34.9</x:v>
+      </x:c>
+      <x:c r="N3" s="76" t="n">
+        <x:v>63.6</x:v>
+      </x:c>
+      <x:c r="O3" s="76" t="n">
+        <x:v>112.1</x:v>
+      </x:c>
+      <x:c r="P3" s="65" t="str">
+        <x:v>偏单体/近身攻击，对群弱。</x:v>
+      </x:c>
       <x:c r="Q3"/>
       <x:c r="R3"/>
       <x:c r="S3"/>
@@ -1157,45 +1391,55 @@
       <x:c r="CC3"/>
       <x:c r="CD3"/>
     </x:row>
-    <x:row r="4" ht="18" customHeight="1">
-      <x:c r="A4" s="31" t="str">
+    <x:row r="4" ht="34.5" customHeight="1">
+      <x:c r="A4" s="75" t="str">
         <x:v>body_barrier</x:v>
       </x:c>
-      <x:c r="B4" s="31" t="str">
+      <x:c r="B4" s="71" t="str">
         <x:v>罩</x:v>
       </x:c>
-      <x:c r="C4" s="31" t="str">
+      <x:c r="C4" s="71" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="D4" s="31" t="str">
+      <x:c r="D4" s="71" t="str">
         <x:v>水</x:v>
       </x:c>
-      <x:c r="E4" s="31" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="31" t="n">
+      <x:c r="E4" s="76" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F4" s="76" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="G4" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G4" s="31" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H4" s="31" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="str">
+      <x:c r="H4" s="76" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I4" s="71" t="str">
         <x:v>3费</x:v>
       </x:c>
-      <x:c r="J4" s="31" t="str">
+      <x:c r="J4" s="71" t="str">
         <x:v>灵器</x:v>
       </x:c>
-      <x:c r="K4" s="31"/>
-      <x:c r="L4" s="31" t="str">
+      <x:c r="K4" s="57" t="str">
+        <x:v>周期释放震荡波，对周围敌人造成伤害，命中敌人时回复生命。</x:v>
+      </x:c>
+      <x:c r="L4" s="71" t="str">
         <x:v>data/artifacts/body_barrier.tres</x:v>
       </x:c>
-      <x:c r="M4"/>
-      <x:c r="N4"/>
-      <x:c r="O4"/>
-      <x:c r="P4"/>
+      <x:c r="M4" s="76" t="n">
+        <x:v>31.7</x:v>
+      </x:c>
+      <x:c r="N4" s="76" t="n">
+        <x:v>57.7</x:v>
+      </x:c>
+      <x:c r="O4" s="76" t="n">
+        <x:v>101.8</x:v>
+      </x:c>
+      <x:c r="P4" s="65" t="str">
+        <x:v>自身范围周期伤害/护盾，贴身全中。</x:v>
+      </x:c>
       <x:c r="Q4"/>
       <x:c r="R4"/>
       <x:c r="S4"/>
@@ -1263,45 +1507,55 @@
       <x:c r="CC4"/>
       <x:c r="CD4"/>
     </x:row>
-    <x:row r="5" ht="18" customHeight="1">
-      <x:c r="A5" s="31" t="str">
+    <x:row r="5" ht="34.5" customHeight="1">
+      <x:c r="A5" s="75" t="str">
         <x:v>brush</x:v>
       </x:c>
-      <x:c r="B5" s="31" t="str">
+      <x:c r="B5" s="71" t="str">
         <x:v>毛笔</x:v>
       </x:c>
-      <x:c r="C5" s="31" t="str">
+      <x:c r="C5" s="71" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="D5" s="31" t="str">
+      <x:c r="D5" s="71" t="str">
         <x:v>木</x:v>
       </x:c>
-      <x:c r="E5" s="31" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F5" s="31" t="n">
+      <x:c r="E5" s="76" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F5" s="76" t="n">
         <x:v>1.21</x:v>
       </x:c>
-      <x:c r="G5" s="31" t="n">
+      <x:c r="G5" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H5" s="31" t="n">
+      <x:c r="H5" s="76" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I5" s="31" t="str">
+      <x:c r="I5" s="71" t="str">
         <x:v>2费</x:v>
       </x:c>
-      <x:c r="J5" s="31" t="str">
+      <x:c r="J5" s="71" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="K5" s="31"/>
-      <x:c r="L5" s="31" t="str">
+      <x:c r="K5" s="57" t="str">
+        <x:v>锁定最近敌人方向挥出直线墨迹，短暂延迟后整条墨迹同时爆发，穿透路径上的所有敌人。</x:v>
+      </x:c>
+      <x:c r="L5" s="71" t="str">
         <x:v>data/artifacts/brush.tres</x:v>
       </x:c>
-      <x:c r="M5"/>
-      <x:c r="N5"/>
-      <x:c r="O5"/>
-      <x:c r="P5"/>
+      <x:c r="M5" s="76" t="n">
+        <x:v>28.1</x:v>
+      </x:c>
+      <x:c r="N5" s="76" t="n">
+        <x:v>51.2</x:v>
+      </x:c>
+      <x:c r="O5" s="76" t="n">
+        <x:v>90.3</x:v>
+      </x:c>
+      <x:c r="P5" s="65" t="str">
+        <x:v>延迟墨线，整条线段判定，线形对群强。</x:v>
+      </x:c>
       <x:c r="Q5"/>
       <x:c r="R5"/>
       <x:c r="S5"/>
@@ -1369,45 +1623,55 @@
       <x:c r="CC5"/>
       <x:c r="CD5"/>
     </x:row>
-    <x:row r="6" ht="18" customHeight="1">
-      <x:c r="A6" s="31" t="str">
+    <x:row r="6" ht="34.5" customHeight="1">
+      <x:c r="A6" s="75" t="str">
         <x:v>copper_coin</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="71" t="str">
         <x:v>铜钱</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="71" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="71" t="str">
         <x:v>金</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F6" s="31" t="n">
+      <x:c r="E6" s="76" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F6" s="76" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="n">
+      <x:c r="G6" s="76" t="n">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="n">
+      <x:c r="H6" s="76" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="71" t="str">
         <x:v>1费</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="71" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="K6" s="31"/>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="K6" s="57" t="str">
+        <x:v>命中后在附近未命中的敌人之间弹射，适合补刀但单体较弱。</x:v>
+      </x:c>
+      <x:c r="L6" s="71" t="str">
         <x:v>data/artifacts/copper_coin.tres</x:v>
       </x:c>
-      <x:c r="M6"/>
-      <x:c r="N6"/>
-      <x:c r="O6"/>
-      <x:c r="P6"/>
+      <x:c r="M6" s="76" t="n">
+        <x:v>22.6</x:v>
+      </x:c>
+      <x:c r="N6" s="76" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="O6" s="76" t="n">
+        <x:v>72.6</x:v>
+      </x:c>
+      <x:c r="P6" s="65" t="str">
+        <x:v>投射物弹射，分散小群表现好。</x:v>
+      </x:c>
       <x:c r="Q6"/>
       <x:c r="R6"/>
       <x:c r="S6"/>
@@ -1475,45 +1739,55 @@
       <x:c r="CC6"/>
       <x:c r="CD6"/>
     </x:row>
-    <x:row r="7" ht="18" customHeight="1">
-      <x:c r="A7" s="31" t="str">
+    <x:row r="7" ht="34.5" customHeight="1">
+      <x:c r="A7" s="75" t="str">
         <x:v>crossbow_puppet</x:v>
       </x:c>
-      <x:c r="B7" s="31" t="str">
+      <x:c r="B7" s="71" t="str">
         <x:v>远程傀儡</x:v>
       </x:c>
-      <x:c r="C7" s="31" t="str">
+      <x:c r="C7" s="71" t="str">
         <x:v>召唤</x:v>
       </x:c>
-      <x:c r="D7" s="31" t="str">
+      <x:c r="D7" s="71" t="str">
         <x:v>雷</x:v>
       </x:c>
-      <x:c r="E7" s="31" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="n">
+      <x:c r="E7" s="76" t="n">
+        <x:v>12.5</x:v>
+      </x:c>
+      <x:c r="F7" s="76" t="n">
         <x:v>2.1</x:v>
       </x:c>
-      <x:c r="G7" s="31" t="n">
+      <x:c r="G7" s="76" t="n">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="H7" s="31" t="n">
+      <x:c r="H7" s="76" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I7" s="31" t="str">
+      <x:c r="I7" s="71" t="str">
         <x:v>1费</x:v>
       </x:c>
-      <x:c r="J7" s="31" t="str">
+      <x:c r="J7" s="71" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="K7" s="31"/>
-      <x:c r="L7" s="31" t="str">
+      <x:c r="K7" s="57" t="str">
+        <x:v>召唤后排远程傀儡，和敌人保持距离并持续发射灵能箭。死亡后会在短时间后重生。</x:v>
+      </x:c>
+      <x:c r="L7" s="71" t="str">
         <x:v>data/artifacts/crossbow_puppet.tres</x:v>
       </x:c>
-      <x:c r="M7"/>
-      <x:c r="N7"/>
-      <x:c r="O7"/>
-      <x:c r="P7"/>
+      <x:c r="M7" s="76" t="n">
+        <x:v>26.3</x:v>
+      </x:c>
+      <x:c r="N7" s="76" t="n">
+        <x:v>51.2</x:v>
+      </x:c>
+      <x:c r="O7" s="76" t="n">
+        <x:v>79.3</x:v>
+      </x:c>
+      <x:c r="P7" s="65" t="str">
+        <x:v>召唤远程单发弩箭，偏单体。</x:v>
+      </x:c>
       <x:c r="Q7"/>
       <x:c r="R7"/>
       <x:c r="S7"/>
@@ -1581,45 +1855,55 @@
       <x:c r="CC7"/>
       <x:c r="CD7"/>
     </x:row>
-    <x:row r="8" ht="18" customHeight="1">
-      <x:c r="A8" s="31" t="str">
+    <x:row r="8" ht="34.5" customHeight="1">
+      <x:c r="A8" s="75" t="str">
         <x:v>dagger</x:v>
       </x:c>
-      <x:c r="B8" s="31" t="str">
+      <x:c r="B8" s="71" t="str">
         <x:v>匕首</x:v>
       </x:c>
-      <x:c r="C8" s="31" t="str">
+      <x:c r="C8" s="71" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="str">
+      <x:c r="D8" s="71" t="str">
         <x:v>毒</x:v>
       </x:c>
-      <x:c r="E8" s="31" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F8" s="31" t="n">
+      <x:c r="E8" s="76" t="n">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="F8" s="76" t="n">
         <x:v>0.21</x:v>
       </x:c>
-      <x:c r="G8" s="31" t="n">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H8" s="31" t="n">
+      <x:c r="G8" s="76" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="76" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I8" s="31" t="str">
+      <x:c r="I8" s="71" t="str">
         <x:v>1费</x:v>
       </x:c>
-      <x:c r="J8" s="31" t="str">
+      <x:c r="J8" s="71" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="K8" s="31"/>
-      <x:c r="L8" s="31" t="str">
+      <x:c r="K8" s="57" t="str">
+        <x:v>高频短距离刺击，可命中少量近身敌人。</x:v>
+      </x:c>
+      <x:c r="L8" s="71" t="str">
         <x:v>data/artifacts/dagger.tres</x:v>
       </x:c>
-      <x:c r="M8"/>
-      <x:c r="N8"/>
-      <x:c r="O8"/>
-      <x:c r="P8"/>
+      <x:c r="M8" s="76" t="n">
+        <x:v>35.7</x:v>
+      </x:c>
+      <x:c r="N8" s="76" t="n">
+        <x:v>65.1</x:v>
+      </x:c>
+      <x:c r="O8" s="76" t="n">
+        <x:v>114.8</x:v>
+      </x:c>
+      <x:c r="P8" s="65" t="str">
+        <x:v>短手高频单体，对群弱。</x:v>
+      </x:c>
       <x:c r="Q8"/>
       <x:c r="R8"/>
       <x:c r="S8"/>
@@ -1687,45 +1971,55 @@
       <x:c r="CC8"/>
       <x:c r="CD8"/>
     </x:row>
-    <x:row r="9" ht="18" customHeight="1">
-      <x:c r="A9" s="31" t="str">
+    <x:row r="9" ht="34.5" customHeight="1">
+      <x:c r="A9" s="75" t="str">
         <x:v>divine_thunder</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="71" t="str">
         <x:v>神雷术</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
+      <x:c r="C9" s="71" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="str">
+      <x:c r="D9" s="71" t="str">
         <x:v>雷</x:v>
       </x:c>
-      <x:c r="E9" s="31" t="n">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F9" s="31" t="n">
+      <x:c r="E9" s="76" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F9" s="76" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G9" s="31" t="n">
+      <x:c r="G9" s="76" t="n">
         <x:v>760</x:v>
       </x:c>
-      <x:c r="H9" s="31" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="str">
+      <x:c r="H9" s="76" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="I9" s="71" t="str">
         <x:v>5费</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="str">
+      <x:c r="J9" s="71" t="str">
         <x:v>仙宝</x:v>
       </x:c>
-      <x:c r="K9" s="31"/>
-      <x:c r="L9" s="31" t="str">
+      <x:c r="K9" s="57" t="str">
+        <x:v>锁定一名敌人降下神雷，以该敌人为中心造成范围伤害。三星时神雷范围大幅增加。</x:v>
+      </x:c>
+      <x:c r="L9" s="71" t="str">
         <x:v>data/artifacts/divine_thunder.tres</x:v>
       </x:c>
-      <x:c r="M9"/>
-      <x:c r="N9"/>
-      <x:c r="O9"/>
-      <x:c r="P9"/>
+      <x:c r="M9" s="76" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="N9" s="76" t="n">
+        <x:v>139.3</x:v>
+      </x:c>
+      <x:c r="O9" s="76" t="n">
+        <x:v>210.1</x:v>
+      </x:c>
+      <x:c r="P9" s="65" t="str">
+        <x:v>锁定点圆形落雷，稳定小范围 AoE。</x:v>
+      </x:c>
       <x:c r="Q9"/>
       <x:c r="R9"/>
       <x:c r="S9"/>
@@ -1793,45 +2087,55 @@
       <x:c r="CC9"/>
       <x:c r="CD9"/>
     </x:row>
-    <x:row r="10" ht="18" customHeight="1">
-      <x:c r="A10" s="31" t="str">
+    <x:row r="10" ht="34.5" customHeight="1">
+      <x:c r="A10" s="75" t="str">
         <x:v>fire_gourd</x:v>
       </x:c>
-      <x:c r="B10" s="31" t="str">
+      <x:c r="B10" s="71" t="str">
         <x:v>火葫芦</x:v>
       </x:c>
-      <x:c r="C10" s="31" t="str">
+      <x:c r="C10" s="71" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="D10" s="31" t="str">
+      <x:c r="D10" s="71" t="str">
         <x:v>火</x:v>
       </x:c>
-      <x:c r="E10" s="31" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F10" s="31" t="n">
+      <x:c r="E10" s="76" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F10" s="76" t="n">
         <x:v>1.18</x:v>
       </x:c>
-      <x:c r="G10" s="31" t="n">
+      <x:c r="G10" s="76" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="H10" s="31" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="str">
+      <x:c r="H10" s="76" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I10" s="71" t="str">
         <x:v>4费</x:v>
       </x:c>
-      <x:c r="J10" s="31" t="str">
+      <x:c r="J10" s="71" t="str">
         <x:v>灵宝</x:v>
       </x:c>
-      <x:c r="K10" s="31"/>
-      <x:c r="L10" s="31" t="str">
+      <x:c r="K10" s="57" t="str">
+        <x:v>向目标方向喷出锥形火焰，对范围内敌人造成伤害。</x:v>
+      </x:c>
+      <x:c r="L10" s="71" t="str">
         <x:v>data/artifacts/fire_gourd.tres</x:v>
       </x:c>
-      <x:c r="M10"/>
-      <x:c r="N10"/>
-      <x:c r="O10"/>
-      <x:c r="P10"/>
+      <x:c r="M10" s="76" t="n">
+        <x:v>60.2</x:v>
+      </x:c>
+      <x:c r="N10" s="76" t="n">
+        <x:v>109.7</x:v>
+      </x:c>
+      <x:c r="O10" s="76" t="n">
+        <x:v>193.4</x:v>
+      </x:c>
+      <x:c r="P10" s="65" t="str">
+        <x:v>前方锥形火焰，对群中强。</x:v>
+      </x:c>
       <x:c r="Q10"/>
       <x:c r="R10"/>
       <x:c r="S10"/>
@@ -1899,45 +2203,55 @@
       <x:c r="CC10"/>
       <x:c r="CD10"/>
     </x:row>
-    <x:row r="11" ht="18" customHeight="1">
-      <x:c r="A11" s="31" t="str">
+    <x:row r="11" ht="34.5" customHeight="1">
+      <x:c r="A11" s="75" t="str">
         <x:v>fire_orb</x:v>
       </x:c>
-      <x:c r="B11" s="31" t="str">
+      <x:c r="B11" s="71" t="str">
         <x:v>法球</x:v>
       </x:c>
-      <x:c r="C11" s="31" t="str">
+      <x:c r="C11" s="71" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="D11" s="31" t="str">
+      <x:c r="D11" s="71" t="str">
         <x:v>火</x:v>
       </x:c>
-      <x:c r="E11" s="31" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F11" s="31" t="n">
+      <x:c r="E11" s="76" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F11" s="76" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="G11" s="31" t="n">
+      <x:c r="G11" s="76" t="n">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="H11" s="31" t="n">
+      <x:c r="H11" s="76" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I11" s="31" t="str">
+      <x:c r="I11" s="71" t="str">
         <x:v>1费</x:v>
       </x:c>
-      <x:c r="J11" s="31" t="str">
+      <x:c r="J11" s="71" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="K11" s="31"/>
-      <x:c r="L11" s="31" t="str">
+      <x:c r="K11" s="57" t="str">
+        <x:v>向最近敌人发射火焰法球，直伤较低，命中后造成小范围爆炸。</x:v>
+      </x:c>
+      <x:c r="L11" s="71" t="str">
         <x:v>data/artifacts/fire_orb.tres</x:v>
       </x:c>
-      <x:c r="M11"/>
-      <x:c r="N11"/>
-      <x:c r="O11"/>
-      <x:c r="P11"/>
+      <x:c r="M11" s="76" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="N11" s="76" t="n">
+        <x:v>43.7</x:v>
+      </x:c>
+      <x:c r="O11" s="76" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="P11" s="65" t="str">
+        <x:v>命中爆炸，聚怪时 AoE 强。</x:v>
+      </x:c>
       <x:c r="Q11"/>
       <x:c r="R11"/>
       <x:c r="S11"/>
@@ -2005,45 +2319,55 @@
       <x:c r="CC11"/>
       <x:c r="CD11"/>
     </x:row>
-    <x:row r="12" ht="18" customHeight="1">
-      <x:c r="A12" s="31" t="str">
+    <x:row r="12" ht="34.5" customHeight="1">
+      <x:c r="A12" s="75" t="str">
         <x:v>fist</x:v>
       </x:c>
-      <x:c r="B12" s="31" t="str">
+      <x:c r="B12" s="71" t="str">
         <x:v>拳</x:v>
       </x:c>
-      <x:c r="C12" s="31" t="str">
+      <x:c r="C12" s="71" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="D12" s="31" t="str">
+      <x:c r="D12" s="71" t="str">
         <x:v>火</x:v>
       </x:c>
-      <x:c r="E12" s="31" t="n">
+      <x:c r="E12" s="76" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F12" s="31" t="n">
+      <x:c r="F12" s="76" t="n">
         <x:v>0.27</x:v>
       </x:c>
-      <x:c r="G12" s="31" t="n">
+      <x:c r="G12" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H12" s="31" t="n">
+      <x:c r="H12" s="76" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I12" s="31" t="str">
+      <x:c r="I12" s="71" t="str">
         <x:v>1费</x:v>
       </x:c>
-      <x:c r="J12" s="31" t="str">
+      <x:c r="J12" s="71" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="K12" s="31"/>
-      <x:c r="L12" s="31" t="str">
+      <x:c r="K12" s="57" t="str">
+        <x:v>快速近身拳劲打击最近敌人，伤害高于远程法宝。</x:v>
+      </x:c>
+      <x:c r="L12" s="71" t="str">
         <x:v>data/artifacts/fist.tres</x:v>
       </x:c>
-      <x:c r="M12"/>
-      <x:c r="N12"/>
-      <x:c r="O12"/>
-      <x:c r="P12"/>
+      <x:c r="M12" s="76" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="N12" s="76" t="n">
+        <x:v>67.5</x:v>
+      </x:c>
+      <x:c r="O12" s="76" t="n">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="P12" s="65" t="str">
+        <x:v>短中距离线形拳劲，对群中等。</x:v>
+      </x:c>
       <x:c r="Q12"/>
       <x:c r="R12"/>
       <x:c r="S12"/>
@@ -2111,45 +2435,55 @@
       <x:c r="CC12"/>
       <x:c r="CD12"/>
     </x:row>
-    <x:row r="13" ht="18" customHeight="1">
-      <x:c r="A13" s="31" t="str">
+    <x:row r="13" ht="34.5" customHeight="1">
+      <x:c r="A13" s="75" t="str">
         <x:v>flying_sword</x:v>
       </x:c>
-      <x:c r="B13" s="31" t="str">
+      <x:c r="B13" s="71" t="str">
         <x:v>飞剑</x:v>
       </x:c>
-      <x:c r="C13" s="31" t="str">
+      <x:c r="C13" s="71" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="D13" s="31" t="str">
+      <x:c r="D13" s="71" t="str">
         <x:v>雷</x:v>
       </x:c>
-      <x:c r="E13" s="31" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F13" s="31" t="n">
+      <x:c r="E13" s="76" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F13" s="76" t="n">
         <x:v>0.68</x:v>
       </x:c>
-      <x:c r="G13" s="31" t="n">
+      <x:c r="G13" s="76" t="n">
         <x:v>560</x:v>
       </x:c>
-      <x:c r="H13" s="31" t="n">
+      <x:c r="H13" s="76" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I13" s="31" t="str">
+      <x:c r="I13" s="71" t="str">
         <x:v>2费</x:v>
       </x:c>
-      <x:c r="J13" s="31" t="str">
+      <x:c r="J13" s="71" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="K13" s="31"/>
-      <x:c r="L13" s="31" t="str">
+      <x:c r="K13" s="57" t="str">
+        <x:v>向最近敌人发射一柄可穿透的飞剑，安全稳定但直伤偏低。</x:v>
+      </x:c>
+      <x:c r="L13" s="71" t="str">
         <x:v>data/artifacts/flying_sword.tres</x:v>
       </x:c>
-      <x:c r="M13"/>
-      <x:c r="N13"/>
-      <x:c r="O13"/>
-      <x:c r="P13"/>
+      <x:c r="M13" s="76" t="n">
+        <x:v>32.4</x:v>
+      </x:c>
+      <x:c r="N13" s="76" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="O13" s="76" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="P13" s="65" t="str">
+        <x:v>穿透投射物，排队敌人时强。</x:v>
+      </x:c>
       <x:c r="Q13"/>
       <x:c r="R13"/>
       <x:c r="S13"/>
@@ -2217,45 +2551,55 @@
       <x:c r="CC13"/>
       <x:c r="CD13"/>
     </x:row>
-    <x:row r="14" ht="18" customHeight="1">
-      <x:c r="A14" s="31" t="str">
+    <x:row r="14" ht="34.5" customHeight="1">
+      <x:c r="A14" s="75" t="str">
         <x:v>ghost</x:v>
       </x:c>
-      <x:c r="B14" s="31" t="str">
+      <x:c r="B14" s="71" t="str">
         <x:v>幽魂</x:v>
       </x:c>
-      <x:c r="C14" s="31" t="str">
+      <x:c r="C14" s="71" t="str">
         <x:v>召唤</x:v>
       </x:c>
-      <x:c r="D14" s="31" t="str">
+      <x:c r="D14" s="71" t="str">
         <x:v>水</x:v>
       </x:c>
-      <x:c r="E14" s="31" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F14" s="31" t="n">
+      <x:c r="E14" s="76" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F14" s="76" t="n">
         <x:v>1.68</x:v>
       </x:c>
-      <x:c r="G14" s="31" t="n">
+      <x:c r="G14" s="76" t="n">
         <x:v>700</x:v>
       </x:c>
-      <x:c r="H14" s="31" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="str">
+      <x:c r="H14" s="76" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I14" s="71" t="str">
         <x:v>4费</x:v>
       </x:c>
-      <x:c r="J14" s="31" t="str">
+      <x:c r="J14" s="71" t="str">
         <x:v>灵宝</x:v>
       </x:c>
-      <x:c r="K14" s="31"/>
-      <x:c r="L14" s="31" t="str">
+      <x:c r="K14" s="57" t="str">
+        <x:v>召唤没有仇恨值的幽魂。幽魂锁定敌人后加速冲击，穿过敌人造成伤害，并在敌人身后短距离停下后重新锁定目标。幽魂不会受到伤害。</x:v>
+      </x:c>
+      <x:c r="L14" s="71" t="str">
         <x:v>data/artifacts/ghost.tres</x:v>
       </x:c>
-      <x:c r="M14"/>
-      <x:c r="N14"/>
-      <x:c r="O14"/>
-      <x:c r="P14"/>
+      <x:c r="M14" s="76" t="n">
+        <x:v>60.5</x:v>
+      </x:c>
+      <x:c r="N14" s="76" t="n">
+        <x:v>90.7</x:v>
+      </x:c>
+      <x:c r="O14" s="76" t="n">
+        <x:v>181.4</x:v>
+      </x:c>
+      <x:c r="P14" s="65" t="str">
+        <x:v>鬼魂冲刺穿过路径敌人，线形对群中等。</x:v>
+      </x:c>
       <x:c r="Q14"/>
       <x:c r="R14"/>
       <x:c r="S14"/>
@@ -2323,45 +2667,55 @@
       <x:c r="CC14"/>
       <x:c r="CD14"/>
     </x:row>
-    <x:row r="15" ht="18" customHeight="1">
-      <x:c r="A15" s="31" t="str">
+    <x:row r="15" ht="34.5" customHeight="1">
+      <x:c r="A15" s="75" t="str">
         <x:v>giant_sword_art</x:v>
       </x:c>
-      <x:c r="B15" s="31" t="str">
+      <x:c r="B15" s="71" t="str">
         <x:v>巨剑术</x:v>
       </x:c>
-      <x:c r="C15" s="31" t="str">
+      <x:c r="C15" s="71" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="D15" s="31" t="str">
+      <x:c r="D15" s="71" t="str">
         <x:v>金</x:v>
       </x:c>
-      <x:c r="E15" s="31" t="n">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F15" s="31" t="n">
+      <x:c r="E15" s="76" t="n">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="F15" s="76" t="n">
         <x:v>1.68</x:v>
       </x:c>
-      <x:c r="G15" s="31" t="n">
+      <x:c r="G15" s="76" t="n">
         <x:v>760</x:v>
       </x:c>
-      <x:c r="H15" s="31" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="str">
+      <x:c r="H15" s="76" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="I15" s="71" t="str">
         <x:v>5费</x:v>
       </x:c>
-      <x:c r="J15" s="31" t="str">
+      <x:c r="J15" s="71" t="str">
         <x:v>仙宝</x:v>
       </x:c>
-      <x:c r="K15" s="31"/>
-      <x:c r="L15" s="31" t="str">
+      <x:c r="K15" s="57" t="str">
+        <x:v>在角色身后凝聚巨剑，朝敌人发射，在较宽的直线范围内造成伤害。三星时以角色为中心横扫一整圈。</x:v>
+      </x:c>
+      <x:c r="L15" s="71" t="str">
         <x:v>data/artifacts/giant_sword_art.tres</x:v>
       </x:c>
-      <x:c r="M15"/>
-      <x:c r="N15"/>
-      <x:c r="O15"/>
-      <x:c r="P15"/>
+      <x:c r="M15" s="76" t="n">
+        <x:v>79.8</x:v>
+      </x:c>
+      <x:c r="N15" s="76" t="n">
+        <x:v>146.9</x:v>
+      </x:c>
+      <x:c r="O15" s="76" t="n">
+        <x:v>225.2</x:v>
+      </x:c>
+      <x:c r="P15" s="65" t="str">
+        <x:v>宽直线穿透飞剑，走廊式对群强。</x:v>
+      </x:c>
       <x:c r="Q15"/>
       <x:c r="R15"/>
       <x:c r="S15"/>
@@ -2429,45 +2783,55 @@
       <x:c r="CC15"/>
       <x:c r="CD15"/>
     </x:row>
-    <x:row r="16" ht="18" customHeight="1">
-      <x:c r="A16" s="31" t="str">
+    <x:row r="16" ht="34.5" customHeight="1">
+      <x:c r="A16" s="75" t="str">
         <x:v>golden_body_avatar</x:v>
       </x:c>
-      <x:c r="B16" s="31" t="str">
+      <x:c r="B16" s="71" t="str">
         <x:v>法相金身</x:v>
       </x:c>
-      <x:c r="C16" s="31" t="str">
+      <x:c r="C16" s="71" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="D16" s="31" t="str">
+      <x:c r="D16" s="71" t="str">
         <x:v>土</x:v>
       </x:c>
-      <x:c r="E16" s="31" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="E16" s="76" t="n">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="F16" s="76" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="G16" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="31" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H16" s="31" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="str">
+      <x:c r="H16" s="76" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="I16" s="71" t="str">
         <x:v>5费</x:v>
       </x:c>
-      <x:c r="J16" s="31" t="str">
+      <x:c r="J16" s="71" t="str">
         <x:v>仙宝</x:v>
       </x:c>
-      <x:c r="K16" s="31"/>
-      <x:c r="L16" s="31" t="str">
+      <x:c r="K16" s="57" t="str">
+        <x:v>角色背后常驻半透明巨大法相，周期砸地造成大范围伤害。</x:v>
+      </x:c>
+      <x:c r="L16" s="71" t="str">
         <x:v>data/artifacts/golden_body_avatar.tres</x:v>
       </x:c>
-      <x:c r="M16"/>
-      <x:c r="N16"/>
-      <x:c r="O16"/>
-      <x:c r="P16"/>
+      <x:c r="M16" s="76" t="n">
+        <x:v>65.8</x:v>
+      </x:c>
+      <x:c r="N16" s="76" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="O16" s="76" t="n">
+        <x:v>211.6</x:v>
+      </x:c>
+      <x:c r="P16" s="65" t="str">
+        <x:v>自身周围法相砸地，近身群怪强。</x:v>
+      </x:c>
       <x:c r="Q16"/>
       <x:c r="R16"/>
       <x:c r="S16"/>
@@ -2535,45 +2899,55 @@
       <x:c r="CC16"/>
       <x:c r="CD16"/>
     </x:row>
-    <x:row r="17" ht="18" customHeight="1">
-      <x:c r="A17" s="31" t="str">
+    <x:row r="17" ht="34.5" customHeight="1">
+      <x:c r="A17" s="75" t="str">
         <x:v>guardian_flying_sword</x:v>
       </x:c>
-      <x:c r="B17" s="31" t="str">
+      <x:c r="B17" s="71" t="str">
         <x:v>护体飞剑</x:v>
       </x:c>
-      <x:c r="C17" s="31" t="str">
+      <x:c r="C17" s="71" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="D17" s="31" t="str">
+      <x:c r="D17" s="71" t="str">
         <x:v>土</x:v>
       </x:c>
-      <x:c r="E17" s="31" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F17" s="31" t="n">
+      <x:c r="E17" s="76" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F17" s="76" t="n">
         <x:v>0.61</x:v>
       </x:c>
-      <x:c r="G17" s="31" t="n">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="H17" s="31" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="str">
+      <x:c r="G17" s="76" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="76" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I17" s="71" t="str">
         <x:v>4费</x:v>
       </x:c>
-      <x:c r="J17" s="31" t="str">
+      <x:c r="J17" s="71" t="str">
         <x:v>灵宝</x:v>
       </x:c>
-      <x:c r="K17" s="31"/>
-      <x:c r="L17" s="31" t="str">
+      <x:c r="K17" s="57" t="str">
+        <x:v>飞剑常驻环绕护身，敌人靠近时会自动刺出反击后返回。</x:v>
+      </x:c>
+      <x:c r="L17" s="71" t="str">
         <x:v>data/artifacts/guardian_flying_sword.tres</x:v>
       </x:c>
-      <x:c r="M17"/>
-      <x:c r="N17"/>
-      <x:c r="O17"/>
-      <x:c r="P17"/>
+      <x:c r="M17" s="76" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="N17" s="76" t="n">
+        <x:v>94.2</x:v>
+      </x:c>
+      <x:c r="O17" s="76" t="n">
+        <x:v>155.4</x:v>
+      </x:c>
+      <x:c r="P17" s="65" t="str">
+        <x:v>环绕飞剑持续刮伤，贴身包围强。</x:v>
+      </x:c>
       <x:c r="Q17"/>
       <x:c r="R17"/>
       <x:c r="S17"/>
@@ -2641,45 +3015,55 @@
       <x:c r="CC17"/>
       <x:c r="CD17"/>
     </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="31" t="str">
+    <x:row r="18" ht="34.5" customHeight="1">
+      <x:c r="A18" s="75" t="str">
         <x:v>guqin</x:v>
       </x:c>
-      <x:c r="B18" s="31" t="str">
+      <x:c r="B18" s="71" t="str">
         <x:v>古琴</x:v>
       </x:c>
-      <x:c r="C18" s="31" t="str">
+      <x:c r="C18" s="71" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="D18" s="31" t="str">
+      <x:c r="D18" s="71" t="str">
         <x:v>水</x:v>
       </x:c>
-      <x:c r="E18" s="31" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F18" s="31" t="n">
+      <x:c r="E18" s="76" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F18" s="76" t="n">
         <x:v>0.82</x:v>
       </x:c>
-      <x:c r="G18" s="31" t="n">
+      <x:c r="G18" s="76" t="n">
         <x:v>480</x:v>
       </x:c>
-      <x:c r="H18" s="31" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="str">
+      <x:c r="H18" s="76" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I18" s="71" t="str">
         <x:v>3费</x:v>
       </x:c>
-      <x:c r="J18" s="31" t="str">
+      <x:c r="J18" s="71" t="str">
         <x:v>灵器</x:v>
       </x:c>
-      <x:c r="K18" s="31"/>
-      <x:c r="L18" s="31" t="str">
+      <x:c r="K18" s="57" t="str">
+        <x:v>音符命中后短暂降低敌人伤害，直伤较低。</x:v>
+      </x:c>
+      <x:c r="L18" s="71" t="str">
         <x:v>data/artifacts/guqin.tres</x:v>
       </x:c>
-      <x:c r="M18"/>
-      <x:c r="N18"/>
-      <x:c r="O18"/>
-      <x:c r="P18"/>
+      <x:c r="M18" s="76" t="n">
+        <x:v>25.6</x:v>
+      </x:c>
+      <x:c r="N18" s="76" t="n">
+        <x:v>46.7</x:v>
+      </x:c>
+      <x:c r="O18" s="76" t="n">
+        <x:v>82.3</x:v>
+      </x:c>
+      <x:c r="P18" s="65" t="str">
+        <x:v>偏辅助/减伤，伤害不是主要价值。</x:v>
+      </x:c>
       <x:c r="Q18"/>
       <x:c r="R18"/>
       <x:c r="S18"/>
@@ -2747,45 +3131,55 @@
       <x:c r="CC18"/>
       <x:c r="CD18"/>
     </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="31" t="str">
+    <x:row r="19" ht="34.5" customHeight="1">
+      <x:c r="A19" s="75" t="str">
         <x:v>heaven_eye</x:v>
       </x:c>
-      <x:c r="B19" s="31" t="str">
+      <x:c r="B19" s="71" t="str">
         <x:v>天眼</x:v>
       </x:c>
-      <x:c r="C19" s="31" t="str">
+      <x:c r="C19" s="71" t="str">
         <x:v>魔修</x:v>
       </x:c>
-      <x:c r="D19" s="31" t="str">
+      <x:c r="D19" s="71" t="str">
         <x:v>水</x:v>
       </x:c>
-      <x:c r="E19" s="31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F19" s="31" t="n">
+      <x:c r="E19" s="76" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F19" s="76" t="n">
         <x:v>2.14</x:v>
       </x:c>
-      <x:c r="G19" s="31" t="n">
+      <x:c r="G19" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H19" s="31" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="str">
+      <x:c r="H19" s="76" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I19" s="71" t="str">
         <x:v>3费</x:v>
       </x:c>
-      <x:c r="J19" s="31" t="str">
+      <x:c r="J19" s="71" t="str">
         <x:v>灵器</x:v>
       </x:c>
-      <x:c r="K19" s="31"/>
-      <x:c r="L19" s="31" t="str">
+      <x:c r="K19" s="57" t="str">
+        <x:v>短时间锁定最近敌人并持续发射天眼光束。攻击期间持续扣除生命，击杀敌人后恢复生命。</x:v>
+      </x:c>
+      <x:c r="L19" s="71" t="str">
         <x:v>data/artifacts/heaven_eye.tres</x:v>
       </x:c>
-      <x:c r="M19"/>
-      <x:c r="N19"/>
-      <x:c r="O19"/>
-      <x:c r="P19"/>
+      <x:c r="M19" s="76" t="n">
+        <x:v>61.7</x:v>
+      </x:c>
+      <x:c r="N19" s="76" t="n">
+        <x:v>112.5</x:v>
+      </x:c>
+      <x:c r="O19" s="76" t="n">
+        <x:v>198.3</x:v>
+      </x:c>
+      <x:c r="P19" s="65" t="str">
+        <x:v>持续光束锁单体，对群弱。</x:v>
+      </x:c>
       <x:c r="Q19"/>
       <x:c r="R19"/>
       <x:c r="S19"/>
@@ -2853,45 +3247,55 @@
       <x:c r="CC19"/>
       <x:c r="CD19"/>
     </x:row>
-    <x:row r="20" ht="18" customHeight="1">
-      <x:c r="A20" s="31" t="str">
+    <x:row r="20" ht="34.5" customHeight="1">
+      <x:c r="A20" s="75" t="str">
         <x:v>iron_guard_puppet</x:v>
       </x:c>
-      <x:c r="B20" s="31" t="str">
+      <x:c r="B20" s="71" t="str">
         <x:v>铁甲傀儡</x:v>
       </x:c>
-      <x:c r="C20" s="31" t="str">
+      <x:c r="C20" s="71" t="str">
         <x:v>召唤</x:v>
       </x:c>
-      <x:c r="D20" s="31" t="str">
+      <x:c r="D20" s="71" t="str">
         <x:v>土</x:v>
       </x:c>
-      <x:c r="E20" s="31" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F20" s="31" t="n">
+      <x:c r="E20" s="76" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F20" s="76" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="G20" s="31" t="n">
+      <x:c r="G20" s="76" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="H20" s="31" t="n">
+      <x:c r="H20" s="76" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I20" s="31" t="str">
+      <x:c r="I20" s="71" t="str">
         <x:v>2费</x:v>
       </x:c>
-      <x:c r="J20" s="31" t="str">
+      <x:c r="J20" s="71" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="K20" s="31"/>
-      <x:c r="L20" s="31" t="str">
+      <x:c r="K20" s="57" t="str">
+        <x:v>召唤高生命铁卫傀儡，尽量挡在玩家与怪群之间，并周期性嘲讽附近敌人。死亡后会重生。</x:v>
+      </x:c>
+      <x:c r="L20" s="71" t="str">
         <x:v>data/artifacts/iron_guard_puppet.tres</x:v>
       </x:c>
-      <x:c r="M20"/>
-      <x:c r="N20"/>
-      <x:c r="O20"/>
-      <x:c r="P20"/>
+      <x:c r="M20" s="76" t="n">
+        <x:v>11.8</x:v>
+      </x:c>
+      <x:c r="N20" s="76" t="n">
+        <x:v>17.6</x:v>
+      </x:c>
+      <x:c r="O20" s="76" t="n">
+        <x:v>35.3</x:v>
+      </x:c>
+      <x:c r="P20" s="65" t="str">
+        <x:v>嘲讽聚怪/控场，攻击偏单体。</x:v>
+      </x:c>
       <x:c r="Q20"/>
       <x:c r="R20"/>
       <x:c r="S20"/>
@@ -2959,45 +3363,55 @@
       <x:c r="CC20"/>
       <x:c r="CD20"/>
     </x:row>
-    <x:row r="21" ht="18" customHeight="1">
-      <x:c r="A21" s="31" t="str">
+    <x:row r="21" ht="34.5" customHeight="1">
+      <x:c r="A21" s="75" t="str">
         <x:v>kick</x:v>
       </x:c>
-      <x:c r="B21" s="31" t="str">
+      <x:c r="B21" s="71" t="str">
         <x:v>腿</x:v>
       </x:c>
-      <x:c r="C21" s="31" t="str">
+      <x:c r="C21" s="71" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="D21" s="31" t="str">
+      <x:c r="D21" s="71" t="str">
         <x:v>土</x:v>
       </x:c>
-      <x:c r="E21" s="31" t="n">
+      <x:c r="E21" s="76" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F21" s="76" t="n">
+        <x:v>0.71</x:v>
+      </x:c>
+      <x:c r="G21" s="76" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H21" s="76" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F21" s="31" t="n">
-        <x:v>0.71</x:v>
-      </x:c>
-      <x:c r="G21" s="31" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H21" s="31" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="str">
+      <x:c r="I21" s="71" t="str">
         <x:v>2费</x:v>
       </x:c>
-      <x:c r="J21" s="31" t="str">
+      <x:c r="J21" s="71" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="K21" s="31"/>
-      <x:c r="L21" s="31" t="str">
+      <x:c r="K21" s="57" t="str">
+        <x:v>贴身旋身扫腿，对周围一圈敌人造成较高伤害并轻微击退。</x:v>
+      </x:c>
+      <x:c r="L21" s="71" t="str">
         <x:v>data/artifacts/kick.tres</x:v>
       </x:c>
-      <x:c r="M21"/>
-      <x:c r="N21"/>
-      <x:c r="O21"/>
-      <x:c r="P21"/>
+      <x:c r="M21" s="76" t="n">
+        <x:v>33.8</x:v>
+      </x:c>
+      <x:c r="N21" s="76" t="n">
+        <x:v>61.6</x:v>
+      </x:c>
+      <x:c r="O21" s="76" t="n">
+        <x:v>108.7</x:v>
+      </x:c>
+      <x:c r="P21" s="65" t="str">
+        <x:v>自身圆形范围，贴身包围强。</x:v>
+      </x:c>
       <x:c r="Q21"/>
       <x:c r="R21"/>
       <x:c r="S21"/>
@@ -3065,45 +3479,55 @@
       <x:c r="CC21"/>
       <x:c r="CD21"/>
     </x:row>
-    <x:row r="22" ht="18" customHeight="1">
-      <x:c r="A22" s="31" t="str">
+    <x:row r="22" ht="34.5" customHeight="1">
+      <x:c r="A22" s="75" t="str">
         <x:v>long_spear</x:v>
       </x:c>
-      <x:c r="B22" s="31" t="str">
+      <x:c r="B22" s="71" t="str">
         <x:v>长枪</x:v>
       </x:c>
-      <x:c r="C22" s="31" t="str">
+      <x:c r="C22" s="71" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="D22" s="31" t="str">
+      <x:c r="D22" s="71" t="str">
         <x:v>金</x:v>
       </x:c>
-      <x:c r="E22" s="31" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F22" s="31" t="n">
+      <x:c r="E22" s="76" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F22" s="76" t="n">
         <x:v>0.75</x:v>
       </x:c>
-      <x:c r="G22" s="31" t="n">
+      <x:c r="G22" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="31" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="str">
+      <x:c r="H22" s="76" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I22" s="71" t="str">
         <x:v>3费</x:v>
       </x:c>
-      <x:c r="J22" s="31" t="str">
+      <x:c r="J22" s="71" t="str">
         <x:v>灵器</x:v>
       </x:c>
-      <x:c r="K22" s="31"/>
-      <x:c r="L22" s="31" t="str">
+      <x:c r="K22" s="57" t="str">
+        <x:v>向最近敌人方向刺出长距离贯穿枪影，适合安全地穿透成排敌人。</x:v>
+      </x:c>
+      <x:c r="L22" s="71" t="str">
         <x:v>data/artifacts/long_spear.tres</x:v>
       </x:c>
-      <x:c r="M22"/>
-      <x:c r="N22"/>
-      <x:c r="O22"/>
-      <x:c r="P22"/>
+      <x:c r="M22" s="76" t="n">
+        <x:v>46.7</x:v>
+      </x:c>
+      <x:c r="N22" s="76" t="n">
+        <x:v>85.1</x:v>
+      </x:c>
+      <x:c r="O22" s="76" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="P22" s="65" t="str">
+        <x:v>正前方长条多目标，队列中等。</x:v>
+      </x:c>
       <x:c r="Q22"/>
       <x:c r="R22"/>
       <x:c r="S22"/>
@@ -3171,45 +3595,55 @@
       <x:c r="CC22"/>
       <x:c r="CD22"/>
     </x:row>
-    <x:row r="23" ht="18" customHeight="1">
-      <x:c r="A23" s="31" t="str">
+    <x:row r="23" ht="34.5" customHeight="1">
+      <x:c r="A23" s="75" t="str">
         <x:v>magic_ring</x:v>
       </x:c>
-      <x:c r="B23" s="31" t="str">
+      <x:c r="B23" s="71" t="str">
         <x:v>法环</x:v>
       </x:c>
-      <x:c r="C23" s="31" t="str">
+      <x:c r="C23" s="71" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="D23" s="31" t="str">
+      <x:c r="D23" s="71" t="str">
         <x:v>水</x:v>
       </x:c>
-      <x:c r="E23" s="31" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F23" s="31" t="n">
+      <x:c r="E23" s="76" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F23" s="76" t="n">
         <x:v>0.89</x:v>
       </x:c>
-      <x:c r="G23" s="31" t="n">
+      <x:c r="G23" s="76" t="n">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="H23" s="31" t="n">
+      <x:c r="H23" s="76" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I23" s="31" t="str">
+      <x:c r="I23" s="71" t="str">
         <x:v>2费</x:v>
       </x:c>
-      <x:c r="J23" s="31" t="str">
+      <x:c r="J23" s="71" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="K23" s="31"/>
-      <x:c r="L23" s="31" t="str">
+      <x:c r="K23" s="57" t="str">
+        <x:v>宽大的法环沿直线缓慢穿透敌人，清线稳定但直伤偏低。</x:v>
+      </x:c>
+      <x:c r="L23" s="71" t="str">
         <x:v>data/artifacts/magic_ring.tres</x:v>
       </x:c>
-      <x:c r="M23"/>
-      <x:c r="N23"/>
-      <x:c r="O23"/>
-      <x:c r="P23"/>
+      <x:c r="M23" s="76" t="n">
+        <x:v>28.1</x:v>
+      </x:c>
+      <x:c r="N23" s="76" t="n">
+        <x:v>51.2</x:v>
+      </x:c>
+      <x:c r="O23" s="76" t="n">
+        <x:v>90.3</x:v>
+      </x:c>
+      <x:c r="P23" s="65" t="str">
+        <x:v>周围环形持续伤害，近身群怪强。</x:v>
+      </x:c>
       <x:c r="Q23"/>
       <x:c r="R23"/>
       <x:c r="S23"/>
@@ -3277,45 +3711,55 @@
       <x:c r="CC23"/>
       <x:c r="CD23"/>
     </x:row>
-    <x:row r="24" ht="18" customHeight="1">
-      <x:c r="A24" s="31" t="str">
+    <x:row r="24" ht="34.5" customHeight="1">
+      <x:c r="A24" s="75" t="str">
         <x:v>one_handed_sword</x:v>
       </x:c>
-      <x:c r="B24" s="31" t="str">
+      <x:c r="B24" s="71" t="str">
         <x:v>单手剑</x:v>
       </x:c>
-      <x:c r="C24" s="31" t="str">
+      <x:c r="C24" s="71" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="D24" s="31" t="str">
+      <x:c r="D24" s="71" t="str">
         <x:v>金</x:v>
       </x:c>
-      <x:c r="E24" s="31" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F24" s="31" t="n">
+      <x:c r="E24" s="76" t="n">
+        <x:v>19.5</x:v>
+      </x:c>
+      <x:c r="F24" s="76" t="n">
         <x:v>0.54</x:v>
       </x:c>
-      <x:c r="G24" s="31" t="n">
+      <x:c r="G24" s="76" t="n">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="H24" s="31" t="n">
+      <x:c r="H24" s="76" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I24" s="31" t="str">
+      <x:c r="I24" s="71" t="str">
         <x:v>1费</x:v>
       </x:c>
-      <x:c r="J24" s="31" t="str">
+      <x:c r="J24" s="71" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="K24" s="31"/>
-      <x:c r="L24" s="31" t="str">
+      <x:c r="K24" s="57" t="str">
+        <x:v>向最近敌人方向挥出近战剑光，伤害和范围都较稳定。</x:v>
+      </x:c>
+      <x:c r="L24" s="71" t="str">
         <x:v>data/artifacts/one_handed_sword.tres</x:v>
       </x:c>
-      <x:c r="M24"/>
-      <x:c r="N24"/>
-      <x:c r="O24"/>
-      <x:c r="P24"/>
+      <x:c r="M24" s="76" t="n">
+        <x:v>36.1</x:v>
+      </x:c>
+      <x:c r="N24" s="76" t="n">
+        <x:v>65.8</x:v>
+      </x:c>
+      <x:c r="O24" s="76" t="n">
+        <x:v>116.1</x:v>
+      </x:c>
+      <x:c r="P24" s="65" t="str">
+        <x:v>短矩形斩击，对群偏弱。</x:v>
+      </x:c>
       <x:c r="Q24"/>
       <x:c r="R24"/>
       <x:c r="S24"/>
@@ -3383,45 +3827,55 @@
       <x:c r="CC24"/>
       <x:c r="CD24"/>
     </x:row>
-    <x:row r="25" ht="18" customHeight="1">
-      <x:c r="A25" s="31" t="str">
+    <x:row r="25" ht="34.5" customHeight="1">
+      <x:c r="A25" s="75" t="str">
         <x:v>palm</x:v>
       </x:c>
-      <x:c r="B25" s="31" t="str">
+      <x:c r="B25" s="71" t="str">
         <x:v>掌</x:v>
       </x:c>
-      <x:c r="C25" s="31" t="str">
+      <x:c r="C25" s="71" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="D25" s="31" t="str">
+      <x:c r="D25" s="71" t="str">
         <x:v>木</x:v>
       </x:c>
-      <x:c r="E25" s="31" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F25" s="31" t="n">
+      <x:c r="E25" s="76" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F25" s="76" t="n">
         <x:v>0.61</x:v>
       </x:c>
-      <x:c r="G25" s="31" t="n">
+      <x:c r="G25" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H25" s="31" t="n">
+      <x:c r="H25" s="76" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I25" s="31" t="str">
+      <x:c r="I25" s="71" t="str">
         <x:v>1费</x:v>
       </x:c>
-      <x:c r="J25" s="31" t="str">
+      <x:c r="J25" s="71" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="K25" s="31"/>
-      <x:c r="L25" s="31" t="str">
+      <x:c r="K25" s="57" t="str">
+        <x:v>挥出掌劲打击前方扇形敌人，并将敌人击退。</x:v>
+      </x:c>
+      <x:c r="L25" s="71" t="str">
         <x:v>data/artifacts/palm.tres</x:v>
       </x:c>
-      <x:c r="M25"/>
-      <x:c r="N25"/>
-      <x:c r="O25"/>
-      <x:c r="P25"/>
+      <x:c r="M25" s="76" t="n">
+        <x:v>27.9</x:v>
+      </x:c>
+      <x:c r="N25" s="76" t="n">
+        <x:v>50.8</x:v>
+      </x:c>
+      <x:c r="O25" s="76" t="n">
+        <x:v>89.6</x:v>
+      </x:c>
+      <x:c r="P25" s="65" t="str">
+        <x:v>宽掌劲/扇面覆盖，近距清群强。</x:v>
+      </x:c>
       <x:c r="Q25"/>
       <x:c r="R25"/>
       <x:c r="S25"/>
@@ -3489,45 +3943,55 @@
       <x:c r="CC25"/>
       <x:c r="CD25"/>
     </x:row>
-    <x:row r="26" ht="18" customHeight="1">
-      <x:c r="A26" s="31" t="str">
+    <x:row r="26" ht="34.5" customHeight="1">
+      <x:c r="A26" s="75" t="str">
         <x:v>poison_bug</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="71" t="str">
         <x:v>毒虫</x:v>
       </x:c>
-      <x:c r="C26" s="31" t="str">
+      <x:c r="C26" s="71" t="str">
         <x:v>召唤</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="str">
+      <x:c r="D26" s="71" t="str">
         <x:v>毒</x:v>
       </x:c>
-      <x:c r="E26" s="31" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F26" s="31" t="n">
+      <x:c r="E26" s="76" t="n">
+        <x:v>9.5</x:v>
+      </x:c>
+      <x:c r="F26" s="76" t="n">
         <x:v>2.8</x:v>
       </x:c>
-      <x:c r="G26" s="31" t="n">
+      <x:c r="G26" s="76" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="H26" s="31" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="str">
+      <x:c r="H26" s="76" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="I26" s="71" t="str">
         <x:v>5费</x:v>
       </x:c>
-      <x:c r="J26" s="31" t="str">
+      <x:c r="J26" s="71" t="str">
         <x:v>仙宝</x:v>
       </x:c>
-      <x:c r="K26" s="31"/>
-      <x:c r="L26" s="31" t="str">
+      <x:c r="K26" s="57" t="str">
+        <x:v>召唤没有仇恨值的毒虫群。毒虫不会被敌人主动攻击，但仍会被范围伤害波及。毒虫近战撕咬并附加中毒。</x:v>
+      </x:c>
+      <x:c r="L26" s="71" t="str">
         <x:v>data/artifacts/poison_bug.tres</x:v>
       </x:c>
-      <x:c r="M26"/>
-      <x:c r="N26"/>
-      <x:c r="O26"/>
-      <x:c r="P26"/>
+      <x:c r="M26" s="76" t="n">
+        <x:v>85.8</x:v>
+      </x:c>
+      <x:c r="N26" s="76" t="n">
+        <x:v>167.6</x:v>
+      </x:c>
+      <x:c r="O26" s="76" t="n">
+        <x:v>255.4</x:v>
+      </x:c>
+      <x:c r="P26" s="65" t="str">
+        <x:v>多只毒虫可分咬多个敌人，持续对群中等。</x:v>
+      </x:c>
       <x:c r="Q26"/>
       <x:c r="R26"/>
       <x:c r="S26"/>
@@ -3595,45 +4059,55 @@
       <x:c r="CC26"/>
       <x:c r="CD26"/>
     </x:row>
-    <x:row r="27" ht="18" customHeight="1">
-      <x:c r="A27" s="31" t="str">
+    <x:row r="27" ht="34.5" customHeight="1">
+      <x:c r="A27" s="75" t="str">
         <x:v>poison_needle</x:v>
       </x:c>
-      <x:c r="B27" s="31" t="str">
+      <x:c r="B27" s="71" t="str">
         <x:v>毒针</x:v>
       </x:c>
-      <x:c r="C27" s="31" t="str">
+      <x:c r="C27" s="71" t="str">
         <x:v>魔修</x:v>
       </x:c>
-      <x:c r="D27" s="31" t="str">
+      <x:c r="D27" s="71" t="str">
         <x:v>毒</x:v>
       </x:c>
-      <x:c r="E27" s="31" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F27" s="31" t="n">
+      <x:c r="E27" s="76" t="n">
+        <x:v>9.5</x:v>
+      </x:c>
+      <x:c r="F27" s="76" t="n">
         <x:v>0.46</x:v>
       </x:c>
-      <x:c r="G27" s="31" t="n">
+      <x:c r="G27" s="76" t="n">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="H27" s="31" t="n">
+      <x:c r="H27" s="76" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I27" s="31" t="str">
+      <x:c r="I27" s="71" t="str">
         <x:v>2费</x:v>
       </x:c>
-      <x:c r="J27" s="31" t="str">
+      <x:c r="J27" s="71" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="K27" s="31"/>
-      <x:c r="L27" s="31" t="str">
+      <x:c r="K27" s="57" t="str">
+        <x:v>高速发射毒针，直接伤害较低，但会让敌人持续中毒。</x:v>
+      </x:c>
+      <x:c r="L27" s="71" t="str">
         <x:v>data/artifacts/poison_needle.tres</x:v>
       </x:c>
-      <x:c r="M27"/>
-      <x:c r="N27"/>
-      <x:c r="O27"/>
-      <x:c r="P27"/>
+      <x:c r="M27" s="76" t="n">
+        <x:v>40.2</x:v>
+      </x:c>
+      <x:c r="N27" s="76" t="n">
+        <x:v>60.7</x:v>
+      </x:c>
+      <x:c r="O27" s="76" t="n">
+        <x:v>94.3</x:v>
+      </x:c>
+      <x:c r="P27" s="65" t="str">
+        <x:v>投射物偏单体，靠叠毒压单点。</x:v>
+      </x:c>
       <x:c r="Q27"/>
       <x:c r="R27"/>
       <x:c r="S27"/>
@@ -3701,45 +4175,55 @@
       <x:c r="CC27"/>
       <x:c r="CD27"/>
     </x:row>
-    <x:row r="28" ht="18" customHeight="1">
-      <x:c r="A28" s="31" t="str">
+    <x:row r="28" ht="34.5" customHeight="1">
+      <x:c r="A28" s="75" t="str">
         <x:v>roar</x:v>
       </x:c>
-      <x:c r="B28" s="31" t="str">
+      <x:c r="B28" s="71" t="str">
         <x:v>吼</x:v>
       </x:c>
-      <x:c r="C28" s="31" t="str">
+      <x:c r="C28" s="71" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="D28" s="31" t="str">
+      <x:c r="D28" s="71" t="str">
         <x:v>雷</x:v>
       </x:c>
-      <x:c r="E28" s="31" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F28" s="31" t="n">
+      <x:c r="E28" s="76" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F28" s="76" t="n">
         <x:v>1.11</x:v>
       </x:c>
-      <x:c r="G28" s="31" t="n">
+      <x:c r="G28" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="31" t="n">
+      <x:c r="H28" s="76" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I28" s="31" t="str">
+      <x:c r="I28" s="71" t="str">
         <x:v>2费</x:v>
       </x:c>
-      <x:c r="J28" s="31" t="str">
+      <x:c r="J28" s="71" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="K28" s="31"/>
-      <x:c r="L28" s="31" t="str">
+      <x:c r="K28" s="57" t="str">
+        <x:v>向目标方向发出锥形声浪，造成伤害并减速敌人。</x:v>
+      </x:c>
+      <x:c r="L28" s="71" t="str">
         <x:v>data/artifacts/roar.tres</x:v>
       </x:c>
-      <x:c r="M28"/>
-      <x:c r="N28"/>
-      <x:c r="O28"/>
-      <x:c r="P28"/>
+      <x:c r="M28" s="76" t="n">
+        <x:v>29.7</x:v>
+      </x:c>
+      <x:c r="N28" s="76" t="n">
+        <x:v>54.2</x:v>
+      </x:c>
+      <x:c r="O28" s="76" t="n">
+        <x:v>95.6</x:v>
+      </x:c>
+      <x:c r="P28" s="65" t="str">
+        <x:v>锥形声浪并减速，控一片敌人。</x:v>
+      </x:c>
       <x:c r="Q28"/>
       <x:c r="R28"/>
       <x:c r="S28"/>
@@ -3807,45 +4291,55 @@
       <x:c r="CC28"/>
       <x:c r="CD28"/>
     </x:row>
-    <x:row r="29" ht="18" customHeight="1">
-      <x:c r="A29" s="31" t="str">
+    <x:row r="29" ht="34.5" customHeight="1">
+      <x:c r="A29" s="75" t="str">
         <x:v>scythe</x:v>
       </x:c>
-      <x:c r="B29" s="31" t="str">
+      <x:c r="B29" s="71" t="str">
         <x:v>镰刀</x:v>
       </x:c>
-      <x:c r="C29" s="31" t="str">
+      <x:c r="C29" s="71" t="str">
         <x:v>魔修</x:v>
       </x:c>
-      <x:c r="D29" s="31" t="str">
+      <x:c r="D29" s="71" t="str">
         <x:v>水</x:v>
       </x:c>
-      <x:c r="E29" s="31" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F29" s="31" t="n">
+      <x:c r="E29" s="76" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F29" s="76" t="n">
         <x:v>1.04</x:v>
       </x:c>
-      <x:c r="G29" s="31" t="n">
+      <x:c r="G29" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="31" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I29" s="31" t="str">
+      <x:c r="H29" s="76" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I29" s="71" t="str">
         <x:v>4费</x:v>
       </x:c>
-      <x:c r="J29" s="31" t="str">
+      <x:c r="J29" s="71" t="str">
         <x:v>灵宝</x:v>
       </x:c>
-      <x:c r="K29" s="31"/>
-      <x:c r="L29" s="31" t="str">
+      <x:c r="K29" s="57" t="str">
+        <x:v>挥动镰刀造成伤害，只有镰刀头部有伤害。造成伤害的一部分会回复生命。</x:v>
+      </x:c>
+      <x:c r="L29" s="71" t="str">
         <x:v>data/artifacts/scythe.tres</x:v>
       </x:c>
-      <x:c r="M29"/>
-      <x:c r="N29"/>
-      <x:c r="O29"/>
-      <x:c r="P29"/>
+      <x:c r="M29" s="76" t="n">
+        <x:v>64.4</x:v>
+      </x:c>
+      <x:c r="N29" s="76" t="n">
+        <x:v>117.5</x:v>
+      </x:c>
+      <x:c r="O29" s="76" t="n">
+        <x:v>207.1</x:v>
+      </x:c>
+      <x:c r="P29" s="65" t="str">
+        <x:v>镰刀范围可命中多敌并吸血。</x:v>
+      </x:c>
       <x:c r="Q29"/>
       <x:c r="R29"/>
       <x:c r="S29"/>
@@ -3913,45 +4407,55 @@
       <x:c r="CC29"/>
       <x:c r="CD29"/>
     </x:row>
-    <x:row r="30" ht="18" customHeight="1">
-      <x:c r="A30" s="31" t="str">
+    <x:row r="30" ht="34.5" customHeight="1">
+      <x:c r="A30" s="75" t="str">
         <x:v>soul_banner</x:v>
       </x:c>
-      <x:c r="B30" s="31" t="str">
+      <x:c r="B30" s="71" t="str">
         <x:v>招魂幡</x:v>
       </x:c>
-      <x:c r="C30" s="31" t="str">
+      <x:c r="C30" s="71" t="str">
         <x:v>魔修</x:v>
       </x:c>
-      <x:c r="D30" s="31" t="str">
+      <x:c r="D30" s="71" t="str">
         <x:v>木</x:v>
       </x:c>
-      <x:c r="E30" s="31" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F30" s="31" t="n">
+      <x:c r="E30" s="76" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F30" s="76" t="n">
         <x:v>2.29</x:v>
       </x:c>
-      <x:c r="G30" s="31" t="n">
+      <x:c r="G30" s="76" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="H30" s="31" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I30" s="31" t="str">
+      <x:c r="H30" s="76" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="I30" s="71" t="str">
         <x:v>5费</x:v>
       </x:c>
-      <x:c r="J30" s="31" t="str">
+      <x:c r="J30" s="71" t="str">
         <x:v>仙宝</x:v>
       </x:c>
-      <x:c r="K30" s="31"/>
-      <x:c r="L30" s="31" t="str">
+      <x:c r="K30" s="57" t="str">
+        <x:v>连接多名敌人并压制，持续造成伤害。敌人死亡后化为幽魂冲击其他敌人，接触后爆炸并消失。</x:v>
+      </x:c>
+      <x:c r="L30" s="71" t="str">
         <x:v>data/artifacts/soul_banner.tres</x:v>
       </x:c>
-      <x:c r="M30"/>
-      <x:c r="N30"/>
-      <x:c r="O30"/>
-      <x:c r="P30"/>
+      <x:c r="M30" s="76" t="n">
+        <x:v>70.3</x:v>
+      </x:c>
+      <x:c r="N30" s="76" t="n">
+        <x:v>128.2</x:v>
+      </x:c>
+      <x:c r="O30" s="76" t="n">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="P30" s="65" t="str">
+        <x:v>连接多个目标，击杀后灵魂爆炸扩散。</x:v>
+      </x:c>
       <x:c r="Q30"/>
       <x:c r="R30"/>
       <x:c r="S30"/>
@@ -4019,45 +4523,55 @@
       <x:c r="CC30"/>
       <x:c r="CD30"/>
     </x:row>
-    <x:row r="31" ht="18" customHeight="1">
-      <x:c r="A31" s="31" t="str">
+    <x:row r="31" ht="34.5" customHeight="1">
+      <x:c r="A31" s="75" t="str">
         <x:v>sword_puppet</x:v>
       </x:c>
-      <x:c r="B31" s="31" t="str">
+      <x:c r="B31" s="71" t="str">
         <x:v>近战傀儡</x:v>
       </x:c>
-      <x:c r="C31" s="31" t="str">
+      <x:c r="C31" s="71" t="str">
         <x:v>召唤</x:v>
       </x:c>
-      <x:c r="D31" s="31" t="str">
+      <x:c r="D31" s="71" t="str">
         <x:v>木</x:v>
       </x:c>
-      <x:c r="E31" s="31" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F31" s="31" t="n">
+      <x:c r="E31" s="76" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F31" s="76" t="n">
         <x:v>1.4</x:v>
       </x:c>
-      <x:c r="G31" s="31" t="n">
+      <x:c r="G31" s="76" t="n">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="H31" s="31" t="n">
+      <x:c r="H31" s="76" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I31" s="31" t="str">
+      <x:c r="I31" s="71" t="str">
         <x:v>1费</x:v>
       </x:c>
-      <x:c r="J31" s="31" t="str">
+      <x:c r="J31" s="71" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="K31" s="31"/>
-      <x:c r="L31" s="31" t="str">
+      <x:c r="K31" s="57" t="str">
+        <x:v>召唤持续存在的近战傀儡，追击最近敌人并用近战挥砍。死亡后会在短时间后重生。</x:v>
+      </x:c>
+      <x:c r="L31" s="71" t="str">
         <x:v>data/artifacts/sword_puppet.tres</x:v>
       </x:c>
-      <x:c r="M31"/>
-      <x:c r="N31"/>
-      <x:c r="O31"/>
-      <x:c r="P31"/>
+      <x:c r="M31" s="76" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="N31" s="76" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="O31" s="76" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="P31" s="65" t="str">
+        <x:v>近战傀儡扇形挥砍，可扫身前小群。</x:v>
+      </x:c>
       <x:c r="Q31"/>
       <x:c r="R31"/>
       <x:c r="S31"/>
@@ -4125,45 +4639,55 @@
       <x:c r="CC31"/>
       <x:c r="CD31"/>
     </x:row>
-    <x:row r="32" ht="18" customHeight="1">
-      <x:c r="A32" s="31" t="str">
+    <x:row r="32" ht="34.5" customHeight="1">
+      <x:c r="A32" s="75" t="str">
         <x:v>thorn_armor</x:v>
       </x:c>
-      <x:c r="B32" s="31" t="str">
+      <x:c r="B32" s="71" t="str">
         <x:v>反甲</x:v>
       </x:c>
-      <x:c r="C32" s="31" t="str">
+      <x:c r="C32" s="71" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="D32" s="31" t="str">
+      <x:c r="D32" s="71" t="str">
         <x:v>金</x:v>
       </x:c>
-      <x:c r="E32" s="31" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F32" s="31" t="n">
+      <x:c r="E32" s="76" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F32" s="76" t="str">
+        <x:v>受击触发</x:v>
+      </x:c>
+      <x:c r="G32" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="31" t="n">
+      <x:c r="H32" s="76" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I32" s="71" t="str">
+        <x:v>4费</x:v>
+      </x:c>
+      <x:c r="J32" s="71" t="str">
+        <x:v>灵宝</x:v>
+      </x:c>
+      <x:c r="K32" s="57" t="str">
+        <x:v>受到伤害时触发，对角色周围敌人造成范围伤害。</x:v>
+      </x:c>
+      <x:c r="L32" s="71" t="str">
+        <x:v>data/artifacts/thorn_armor.tres</x:v>
+      </x:c>
+      <x:c r="M32" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="31" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I32" s="31" t="str">
-        <x:v>4费</x:v>
-      </x:c>
-      <x:c r="J32" s="31" t="str">
-        <x:v>灵宝</x:v>
-      </x:c>
-      <x:c r="K32" s="31"/>
-      <x:c r="L32" s="31" t="str">
-        <x:v>data/artifacts/thorn_armor.tres</x:v>
-      </x:c>
-      <x:c r="M32"/>
-      <x:c r="N32"/>
-      <x:c r="O32"/>
-      <x:c r="P32"/>
+      <x:c r="N32" s="76" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O32" s="76" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P32" s="65" t="str">
+        <x:v>受击触发范围反伤，按触发频率体现价值。</x:v>
+      </x:c>
       <x:c r="Q32"/>
       <x:c r="R32"/>
       <x:c r="S32"/>
@@ -4231,45 +4755,55 @@
       <x:c r="CC32"/>
       <x:c r="CD32"/>
     </x:row>
-    <x:row r="33" ht="18" customHeight="1">
-      <x:c r="A33" s="31" t="str">
+    <x:row r="33" ht="34.5" customHeight="1">
+      <x:c r="A33" s="75" t="str">
         <x:v>turret</x:v>
       </x:c>
-      <x:c r="B33" s="31" t="str">
+      <x:c r="B33" s="71" t="str">
         <x:v>炮台</x:v>
       </x:c>
-      <x:c r="C33" s="31" t="str">
+      <x:c r="C33" s="71" t="str">
         <x:v>召唤</x:v>
       </x:c>
-      <x:c r="D33" s="31" t="str">
+      <x:c r="D33" s="71" t="str">
         <x:v>火</x:v>
       </x:c>
-      <x:c r="E33" s="31" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F33" s="31" t="n">
+      <x:c r="E33" s="76" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F33" s="76" t="n">
         <x:v>1.12</x:v>
       </x:c>
-      <x:c r="G33" s="31" t="n">
+      <x:c r="G33" s="76" t="n">
         <x:v>700</x:v>
       </x:c>
-      <x:c r="H33" s="31" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I33" s="31" t="str">
+      <x:c r="H33" s="76" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I33" s="71" t="str">
         <x:v>3费</x:v>
       </x:c>
-      <x:c r="J33" s="31" t="str">
+      <x:c r="J33" s="71" t="str">
         <x:v>灵器</x:v>
       </x:c>
-      <x:c r="K33" s="31"/>
-      <x:c r="L33" s="31" t="str">
+      <x:c r="K33" s="57" t="str">
+        <x:v>召唤固定炮台自动索敌并发射爆炸炮弹。玩家离开过远时，炮台会延迟重新部署到玩家附近。</x:v>
+      </x:c>
+      <x:c r="L33" s="71" t="str">
         <x:v>data/artifacts/turret.tres</x:v>
       </x:c>
-      <x:c r="M33"/>
-      <x:c r="N33"/>
-      <x:c r="O33"/>
-      <x:c r="P33"/>
+      <x:c r="M33" s="76" t="n">
+        <x:v>43.7</x:v>
+      </x:c>
+      <x:c r="N33" s="76" t="n">
+        <x:v>65.5</x:v>
+      </x:c>
+      <x:c r="O33" s="76" t="n">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="P33" s="65" t="str">
+        <x:v>炮台爆炸弹，阵地 AoE 强。</x:v>
+      </x:c>
       <x:c r="Q33"/>
       <x:c r="R33"/>
       <x:c r="S33"/>
@@ -4337,45 +4871,55 @@
       <x:c r="CC33"/>
       <x:c r="CD33"/>
     </x:row>
-    <x:row r="34" ht="18" customHeight="1">
-      <x:c r="A34" s="31" t="str">
+    <x:row r="34" ht="34.5" customHeight="1">
+      <x:c r="A34" s="77" t="str">
         <x:v>two_handed_sword</x:v>
       </x:c>
-      <x:c r="B34" s="31" t="str">
+      <x:c r="B34" s="72" t="str">
         <x:v>双手剑</x:v>
       </x:c>
-      <x:c r="C34" s="31" t="str">
+      <x:c r="C34" s="72" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="D34" s="31" t="str">
+      <x:c r="D34" s="72" t="str">
         <x:v>土</x:v>
       </x:c>
-      <x:c r="E34" s="31" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F34" s="31" t="n">
+      <x:c r="E34" s="78" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F34" s="78" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="G34" s="31" t="n">
+      <x:c r="G34" s="78" t="n">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="H34" s="31" t="n">
+      <x:c r="H34" s="78" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I34" s="31" t="str">
+      <x:c r="I34" s="72" t="str">
         <x:v>2费</x:v>
       </x:c>
-      <x:c r="J34" s="31" t="str">
+      <x:c r="J34" s="72" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="K34" s="31"/>
-      <x:c r="L34" s="31" t="str">
+      <x:c r="K34" s="61" t="str">
+        <x:v>以较慢节奏挥出沉重剑光，造成高伤害的大范围扇形斩击。</x:v>
+      </x:c>
+      <x:c r="L34" s="72" t="str">
         <x:v>data/artifacts/two_handed_sword.tres</x:v>
       </x:c>
-      <x:c r="M34"/>
-      <x:c r="N34"/>
-      <x:c r="O34"/>
-      <x:c r="P34"/>
+      <x:c r="M34" s="78" t="n">
+        <x:v>36.5</x:v>
+      </x:c>
+      <x:c r="N34" s="78" t="n">
+        <x:v>66.5</x:v>
+      </x:c>
+      <x:c r="O34" s="78" t="n">
+        <x:v>117.2</x:v>
+      </x:c>
+      <x:c r="P34" s="66" t="str">
+        <x:v>近战矩形大挥砍，可命中路径内多个敌人。</x:v>
+      </x:c>
       <x:c r="Q34"/>
       <x:c r="R34"/>
       <x:c r="S34"/>
@@ -4446,149 +4990,12 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ff8f219dd864007"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3995b4025734816"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl\worksheets\sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="18"/>
-  <x:cols>
-    <x:col min="1" max="1" width="10" customWidth="1"/>
-    <x:col min="2" max="2" width="16" customWidth="1"/>
-    <x:col min="3" max="3" width="22" customWidth="1"/>
-    <x:col min="4" max="4" width="62" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="22" customHeight="1">
-      <x:c r="A1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>关卡</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>类型</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>奖励/作用</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>备注</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="31" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B2" s="31" t="inlineStr">
-        <x:is>
-          <x:t>Boss关</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" s="31" t="inlineStr">
-        <x:is>
-          <x:t>筑基材料</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" s="31" t="inlineStr">
-        <x:is>
-          <x:t>Boss关也会继续刷小怪；击败Boss后进入奇遇选择，再进商店</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="31" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B3" s="31" t="inlineStr">
-        <x:is>
-          <x:t>Boss关</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" s="31" t="inlineStr">
-        <x:is>
-          <x:t>结丹材料</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" s="31" t="inlineStr">
-        <x:is>
-          <x:t>Boss关也会继续刷小怪；击败Boss后进入奇遇选择，再进商店</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="31" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B4" s="31" t="inlineStr">
-        <x:is>
-          <x:t>Boss关</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="31" t="inlineStr">
-        <x:is>
-          <x:t>元婴材料</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="31" t="inlineStr">
-        <x:is>
-          <x:t>Boss关也会继续刷小怪；击败Boss后进入奇遇选择，再进商店</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="22" customHeight="1">
-      <x:c r="A5" s="31" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B5" s="31" t="inlineStr">
-        <x:is>
-          <x:t>Boss关</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="31" t="inlineStr">
-        <x:is>
-          <x:t>化神材料</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="31" t="inlineStr">
-        <x:is>
-          <x:t>Boss关也会继续刷小怪；击败Boss后进入奇遇选择，再进商店</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="31" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B6" s="31" t="inlineStr">
-        <x:is>
-          <x:t>关底Boss</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="31" t="inlineStr">
-        <x:is>
-          <x:t>通关结算</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" s="31" t="inlineStr">
-        <x:is>
-          <x:t>最终Boss；击败后直接通关</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
@@ -5743,12 +6150,12 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e92b6f553574965"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b2aa801cca041bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
@@ -5975,12 +6382,12 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd80cf5b0f7c456a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7eb2055c5b9242f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
@@ -6491,13 +6898,13 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8d4ac1ce0e046ca"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b6d198288184b9c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcd4e7a59807466e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R121ec0a8ee3a45e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:sheetData>
@@ -6513,7 +6920,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl\worksheets\sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -6604,7 +7011,7 @@
       <x:c r="G2" s="31" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H2" s="31"/>
+      <x:c r="H2" s="31" t="str"/>
       <x:c r="I2"/>
       <x:c r="J2"/>
       <x:c r="K2"/>
@@ -6639,7 +7046,7 @@
       <x:c r="G3" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H3" s="31"/>
+      <x:c r="H3" s="31" t="str"/>
       <x:c r="I3"/>
       <x:c r="J3"/>
       <x:c r="K3"/>
@@ -6672,9 +7079,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G4" s="31" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H4" s="31"/>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H4" s="31" t="str"/>
       <x:c r="I4"/>
       <x:c r="J4"/>
       <x:c r="K4"/>
@@ -6709,7 +7116,7 @@
       <x:c r="G5" s="31" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H5" s="31"/>
+      <x:c r="H5" s="31" t="str"/>
       <x:c r="I5"/>
       <x:c r="J5"/>
       <x:c r="K5"/>
@@ -6744,7 +7151,7 @@
       <x:c r="G6" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H6" s="31"/>
+      <x:c r="H6" s="31" t="str"/>
       <x:c r="I6"/>
       <x:c r="J6"/>
       <x:c r="K6"/>
@@ -6779,7 +7186,7 @@
       <x:c r="G7" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H7" s="31"/>
+      <x:c r="H7" s="31" t="str"/>
       <x:c r="I7"/>
       <x:c r="J7"/>
       <x:c r="K7"/>
@@ -6814,7 +7221,7 @@
       <x:c r="G8" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H8" s="31"/>
+      <x:c r="H8" s="31" t="str"/>
       <x:c r="I8"/>
       <x:c r="J8"/>
       <x:c r="K8"/>
@@ -6847,9 +7254,9 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="G9" s="31" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H9" s="31"/>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H9" s="31" t="str"/>
       <x:c r="I9"/>
       <x:c r="J9"/>
       <x:c r="K9"/>
@@ -6882,9 +7289,9 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="G10" s="31" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H10" s="31"/>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H10" s="31" t="str"/>
       <x:c r="I10"/>
       <x:c r="J10"/>
       <x:c r="K10"/>
@@ -6919,7 +7326,7 @@
       <x:c r="G11" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H11" s="31"/>
+      <x:c r="H11" s="31" t="str"/>
       <x:c r="I11"/>
       <x:c r="J11"/>
       <x:c r="K11"/>
@@ -6954,7 +7361,7 @@
       <x:c r="G12" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H12" s="31"/>
+      <x:c r="H12" s="31" t="str"/>
       <x:c r="I12"/>
       <x:c r="J12"/>
       <x:c r="K12"/>
@@ -6989,7 +7396,7 @@
       <x:c r="G13" s="31" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H13" s="31"/>
+      <x:c r="H13" s="31" t="str"/>
       <x:c r="I13"/>
       <x:c r="J13"/>
       <x:c r="K13"/>
@@ -7022,9 +7429,9 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="G14" s="31" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H14" s="31"/>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H14" s="31" t="str"/>
       <x:c r="I14"/>
       <x:c r="J14"/>
       <x:c r="K14"/>
@@ -7057,9 +7464,9 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="G15" s="31" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H15" s="31"/>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H15" s="31" t="str"/>
       <x:c r="I15"/>
       <x:c r="J15"/>
       <x:c r="K15"/>
@@ -7092,9 +7499,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G16" s="31" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H16" s="31"/>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H16" s="31" t="str"/>
       <x:c r="I16"/>
       <x:c r="J16"/>
       <x:c r="K16"/>
@@ -7127,9 +7534,9 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G17" s="31" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H17" s="31"/>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H17" s="31" t="str"/>
       <x:c r="I17"/>
       <x:c r="J17"/>
       <x:c r="K17"/>
@@ -7162,9 +7569,9 @@
         <x:v>480</x:v>
       </x:c>
       <x:c r="G18" s="31" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H18" s="31"/>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H18" s="31" t="str"/>
       <x:c r="I18"/>
       <x:c r="J18"/>
       <x:c r="K18"/>
@@ -7197,9 +7604,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G19" s="31" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H19" s="31"/>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H19" s="31" t="str"/>
       <x:c r="I19"/>
       <x:c r="J19"/>
       <x:c r="K19"/>
@@ -7234,7 +7641,7 @@
       <x:c r="G20" s="31" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H20" s="31"/>
+      <x:c r="H20" s="31" t="str"/>
       <x:c r="I20"/>
       <x:c r="J20"/>
       <x:c r="K20"/>
@@ -7269,7 +7676,7 @@
       <x:c r="G21" s="31" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H21" s="31"/>
+      <x:c r="H21" s="31" t="str"/>
       <x:c r="I21"/>
       <x:c r="J21"/>
       <x:c r="K21"/>
@@ -7302,9 +7709,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G22" s="31" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H22" s="31"/>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H22" s="31" t="str"/>
       <x:c r="I22"/>
       <x:c r="J22"/>
       <x:c r="K22"/>
@@ -7339,7 +7746,7 @@
       <x:c r="G23" s="31" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H23" s="31"/>
+      <x:c r="H23" s="31" t="str"/>
       <x:c r="I23"/>
       <x:c r="J23"/>
       <x:c r="K23"/>
@@ -7374,7 +7781,7 @@
       <x:c r="G24" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H24" s="31"/>
+      <x:c r="H24" s="31" t="str"/>
       <x:c r="I24"/>
       <x:c r="J24"/>
       <x:c r="K24"/>
@@ -7409,7 +7816,7 @@
       <x:c r="G25" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H25" s="31"/>
+      <x:c r="H25" s="31" t="str"/>
       <x:c r="I25"/>
       <x:c r="J25"/>
       <x:c r="K25"/>
@@ -7442,9 +7849,9 @@
         <x:v>450</x:v>
       </x:c>
       <x:c r="G26" s="31" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H26" s="31"/>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H26" s="31" t="str"/>
       <x:c r="I26"/>
       <x:c r="J26"/>
       <x:c r="K26"/>
@@ -7479,7 +7886,7 @@
       <x:c r="G27" s="31" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H27" s="31"/>
+      <x:c r="H27" s="31" t="str"/>
       <x:c r="I27"/>
       <x:c r="J27"/>
       <x:c r="K27"/>
@@ -7514,7 +7921,7 @@
       <x:c r="G28" s="31" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H28" s="31"/>
+      <x:c r="H28" s="31" t="str"/>
       <x:c r="I28"/>
       <x:c r="J28"/>
       <x:c r="K28"/>
@@ -7547,9 +7954,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G29" s="31" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H29" s="31"/>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H29" s="31" t="str"/>
       <x:c r="I29"/>
       <x:c r="J29"/>
       <x:c r="K29"/>
@@ -7582,9 +7989,9 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="G30" s="31" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H30" s="31"/>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H30" s="31" t="str"/>
       <x:c r="I30"/>
       <x:c r="J30"/>
       <x:c r="K30"/>
@@ -7619,7 +8026,7 @@
       <x:c r="G31" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H31" s="31"/>
+      <x:c r="H31" s="31" t="str"/>
       <x:c r="I31"/>
       <x:c r="J31"/>
       <x:c r="K31"/>
@@ -7652,9 +8059,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G32" s="31" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H32" s="31"/>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H32" s="31" t="str"/>
       <x:c r="I32"/>
       <x:c r="J32"/>
       <x:c r="K32"/>
@@ -7687,9 +8094,9 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="G33" s="31" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H33" s="31"/>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H33" s="31" t="str"/>
       <x:c r="I33"/>
       <x:c r="J33"/>
       <x:c r="K33"/>
@@ -7724,7 +8131,7 @@
       <x:c r="G34" s="31" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H34" s="31"/>
+      <x:c r="H34" s="31" t="str"/>
       <x:c r="I34"/>
       <x:c r="J34"/>
       <x:c r="K34"/>
@@ -8198,13 +8605,13 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ff111ae40724b09"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ed0a1f020e8409e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R210b5827bb8b4137"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b5981e0068b4ba6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl\worksheets\sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -8268,7 +8675,7 @@
         <x:v>灵石</x:v>
       </x:c>
       <x:c r="E2" s="31" t="str">
-        <x:v>仍可口头称为1-5费，实际价格10/20/40/60/100</x:v>
+        <x:v>仍可口头称为1-5费，实际价格10-50</x:v>
       </x:c>
       <x:c r="F2"/>
     </x:row>
@@ -8286,7 +8693,7 @@
         <x:v>灵石</x:v>
       </x:c>
       <x:c r="E3" s="31" t="str">
-        <x:v>仍可口头称为1-5费，实际价格10/20/40/60/100</x:v>
+        <x:v>仍可口头称为1-5费，实际价格10-50</x:v>
       </x:c>
       <x:c r="F3"/>
     </x:row>
@@ -8298,13 +8705,13 @@
         <x:v>3费</x:v>
       </x:c>
       <x:c r="C4" s="31" t="n">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D4" s="31" t="str">
         <x:v>灵石</x:v>
       </x:c>
       <x:c r="E4" s="31" t="str">
-        <x:v>仍可口头称为1-5费，实际价格10/20/40/60/100</x:v>
+        <x:v>仍可口头称为1-5费，实际价格10-50</x:v>
       </x:c>
       <x:c r="F4"/>
     </x:row>
@@ -8316,13 +8723,13 @@
         <x:v>4费</x:v>
       </x:c>
       <x:c r="C5" s="31" t="n">
-        <x:v>60</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D5" s="31" t="str">
         <x:v>灵石</x:v>
       </x:c>
       <x:c r="E5" s="31" t="str">
-        <x:v>仍可口头称为1-5费，实际价格10/20/40/60/100</x:v>
+        <x:v>仍可口头称为1-5费，实际价格10-50</x:v>
       </x:c>
       <x:c r="F5"/>
     </x:row>
@@ -8334,13 +8741,13 @@
         <x:v>5费</x:v>
       </x:c>
       <x:c r="C6" s="31" t="n">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D6" s="31" t="str">
         <x:v>灵石</x:v>
       </x:c>
       <x:c r="E6" s="31" t="str">
-        <x:v>仍可口头称为1-5费，实际价格10/20/40/60/100</x:v>
+        <x:v>仍可口头称为1-5费，实际价格10-50</x:v>
       </x:c>
       <x:c r="F6"/>
     </x:row>
@@ -8352,13 +8759,13 @@
         <x:v>初始灵石</x:v>
       </x:c>
       <x:c r="C7" s="31" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D7" s="31" t="str">
         <x:v>灵石</x:v>
       </x:c>
       <x:c r="E7" s="31" t="str">
-        <x:v>初始可购买两个1费法宝</x:v>
+        <x:v>可购买一个1费法宝</x:v>
       </x:c>
       <x:c r="F7"/>
     </x:row>
@@ -8616,7 +9023,7 @@
         <x:v>初始刷新</x:v>
       </x:c>
       <x:c r="C22" s="31" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D22" s="31" t="str">
         <x:v>灵石</x:v>
@@ -8634,13 +9041,13 @@
         <x:v>第n次刷新</x:v>
       </x:c>
       <x:c r="C23" s="31" t="str">
-        <x:v>5 × n</x:v>
+        <x:v>n</x:v>
       </x:c>
       <x:c r="D23" s="31" t="str">
         <x:v>灵石</x:v>
       </x:c>
       <x:c r="E23" s="31" t="str">
-        <x:v>第1次=5，第2次=10，第3次=15，逐次+5</x:v>
+        <x:v>第1次=1，第2次=2，逐次+1</x:v>
       </x:c>
       <x:c r="F23"/>
     </x:row>
@@ -8658,7 +9065,7 @@
         <x:v>灵石/修为</x:v>
       </x:c>
       <x:c r="E24" s="31" t="str">
-        <x:v>12次点击，满120后需筑基材料突破</x:v>
+        <x:v>12次点击，满120自动突破</x:v>
       </x:c>
       <x:c r="F24"/>
     </x:row>
@@ -8676,7 +9083,7 @@
         <x:v>灵石/修为</x:v>
       </x:c>
       <x:c r="E25" s="31" t="str">
-        <x:v>12次点击，满240后需结丹材料突破</x:v>
+        <x:v>12次点击，满240自动突破</x:v>
       </x:c>
       <x:c r="F25"/>
     </x:row>
@@ -8694,7 +9101,7 @@
         <x:v>灵石/修为</x:v>
       </x:c>
       <x:c r="E26" s="31" t="str">
-        <x:v>10次点击，满400后需元婴材料突破</x:v>
+        <x:v>10次点击，满400自动突破</x:v>
       </x:c>
       <x:c r="F26"/>
     </x:row>
@@ -8712,7 +9119,7 @@
         <x:v>灵石/修为</x:v>
       </x:c>
       <x:c r="E27" s="31" t="str">
-        <x:v>10次点击，满600后需化神材料突破</x:v>
+        <x:v>10次点击，满600自动突破</x:v>
       </x:c>
       <x:c r="F27"/>
     </x:row>
@@ -8978,1108 +9385,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03391997067a418b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R876184d3a19d4c6e"/>
   </x:tableParts>
 </x:worksheet>
-</file>
-
-<file path=xl\worksheets\sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="18"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" customWidth="1"/>
-    <x:col min="2" max="2" width="18" customWidth="1"/>
-    <x:col min="3" max="3" width="14" customWidth="1"/>
-    <x:col min="4" max="4" width="18" customWidth="1"/>
-    <x:col min="5" max="5" width="46" customWidth="1"/>
-    <x:col min="6" max="6" width="26" customWidth="1"/>
-    <x:col min="7" max="7" width="42" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="22" customHeight="1">
-      <x:c r="A1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>ID</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>名称</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>类型</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>触发时机</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>效果</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>数值/持续</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>实现备注</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="31" t="inlineStr">
-        <x:is>
-          <x:t>treasure_body</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="31" t="inlineStr">
-        <x:is>
-          <x:t>聚宝灵体</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" s="31" t="inlineStr">
-        <x:is>
-          <x:t>天命</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" s="31" t="inlineStr">
-        <x:is>
-          <x:t>开局三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E2" s="31" t="inlineStr">
-        <x:is>
-          <x:t>开局获得50灵石；前5关法宝价格-50%</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F2" s="31" t="inlineStr">
-        <x:is>
-          <x:t>+50灵石；第0-4个已清关商店价格x0.5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G2" s="31" t="inlineStr">
-        <x:is>
-          <x:t>与其他价格倍率乘算</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="31" t="inlineStr">
-        <x:is>
-          <x:t>loose_cultivator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" s="31" t="inlineStr">
-        <x:is>
-          <x:t>散修</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" s="31" t="inlineStr">
-        <x:is>
-          <x:t>天命</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" s="31" t="inlineStr">
-        <x:is>
-          <x:t>开局三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E3" s="31" t="inlineStr">
-        <x:is>
-          <x:t>法宝价格-20%；刷新价格+40%</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F3" s="31" t="inlineStr">
-        <x:is>
-          <x:t>购买价格x0.8；刷新价格x1.4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G3" s="31" t="inlineStr">
-        <x:is>
-          <x:t>刷新向上取整</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="31" t="inlineStr">
-        <x:is>
-          <x:t>trade_genius</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="31" t="inlineStr">
-        <x:is>
-          <x:t>经商天才</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="31" t="inlineStr">
-        <x:is>
-          <x:t>天命</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="31" t="inlineStr">
-        <x:is>
-          <x:t>开局三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" s="31" t="inlineStr">
-        <x:is>
-          <x:t>每次商店额外出现1件法宝</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" s="31" t="inlineStr">
-        <x:is>
-          <x:t>商店商品数+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" s="31" t="inlineStr">
-        <x:is>
-          <x:t>默认5件，变6件</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="22" customHeight="1">
-      <x:c r="A5" s="31" t="inlineStr">
-        <x:is>
-          <x:t>late_bloomer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="31" t="inlineStr">
-        <x:is>
-          <x:t>大器晚成</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="31" t="inlineStr">
-        <x:is>
-          <x:t>天命</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="31" t="inlineStr">
-        <x:is>
-          <x:t>开局三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="31" t="inlineStr">
-        <x:is>
-          <x:t>伤害-30%；每过一关伤害+3%</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="31" t="inlineStr">
-        <x:is>
-          <x:t>初始伤害x0.7；每已清关+0.03</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="31" t="inlineStr">
-        <x:is>
-          <x:t>与奇遇伤害倍率乘算</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="31" t="inlineStr">
-        <x:is>
-          <x:t>broken_body</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="31" t="inlineStr">
-        <x:is>
-          <x:t>残缺道体</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="31" t="inlineStr">
-        <x:is>
-          <x:t>天命</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" s="31" t="inlineStr">
-        <x:is>
-          <x:t>开局三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E6" s="31" t="inlineStr">
-        <x:is>
-          <x:t>最大生命值-30%；伤害+50%</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F6" s="31" t="inlineStr">
-        <x:is>
-          <x:t>最大生命x0.7；伤害x1.5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G6" s="31" t="inlineStr">
-        <x:is>
-          <x:t>最大生命与体修生命倍率乘算</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl\worksheets\sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="18"/>
-  <x:cols>
-    <x:col min="1" max="1" width="8" customWidth="1"/>
-    <x:col min="2" max="2" width="24" customWidth="1"/>
-    <x:col min="3" max="3" width="18" customWidth="1"/>
-    <x:col min="4" max="4" width="14" customWidth="1"/>
-    <x:col min="5" max="5" width="20" customWidth="1"/>
-    <x:col min="6" max="6" width="46" customWidth="1"/>
-    <x:col min="7" max="7" width="24" customWidth="1"/>
-    <x:col min="8" max="8" width="42" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="22" customHeight="1">
-      <x:c r="A1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>编号</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>ID</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>名称</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>分类</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>出现时机</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>效果</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>数值/持续</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H1" s="47" t="inlineStr">
-        <x:is>
-          <x:t>实现备注</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="31" t="inlineStr">
-        <x:is>
-          <x:t>bonus_sword</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" s="31" t="inlineStr">
-        <x:is>
-          <x:t>剑心顿悟</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" s="31" t="inlineStr">
-        <x:is>
-          <x:t>羁绊</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E2" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F2" s="31" t="inlineStr">
-        <x:is>
-          <x:t>剑修激活数+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G2" s="31" t="inlineStr">
-        <x:is>
-          <x:t>永久+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H2" s="31" t="inlineStr">
-        <x:is>
-          <x:t>计入羁绊UI和阈值</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="31" t="inlineStr">
-        <x:is>
-          <x:t>bonus_magic</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" s="31" t="inlineStr">
-        <x:is>
-          <x:t>法意流转</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" s="31" t="inlineStr">
-        <x:is>
-          <x:t>羁绊</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E3" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F3" s="31" t="inlineStr">
-        <x:is>
-          <x:t>法修激活数+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G3" s="31" t="inlineStr">
-        <x:is>
-          <x:t>永久+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H3" s="31" t="inlineStr">
-        <x:is>
-          <x:t>计入羁绊UI和阈值</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B4" s="31" t="inlineStr">
-        <x:is>
-          <x:t>bonus_body</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="31" t="inlineStr">
-        <x:is>
-          <x:t>淬体机缘</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="31" t="inlineStr">
-        <x:is>
-          <x:t>羁绊</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" s="31" t="inlineStr">
-        <x:is>
-          <x:t>体修激活数+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" s="31" t="inlineStr">
-        <x:is>
-          <x:t>永久+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H4" s="31" t="inlineStr">
-        <x:is>
-          <x:t>计入羁绊UI和阈值</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="22" customHeight="1">
-      <x:c r="A5" s="31" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B5" s="31" t="inlineStr">
-        <x:is>
-          <x:t>bonus_summon</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="31" t="inlineStr">
-        <x:is>
-          <x:t>役灵契机</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="31" t="inlineStr">
-        <x:is>
-          <x:t>羁绊</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="31" t="inlineStr">
-        <x:is>
-          <x:t>召唤激活数+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="31" t="inlineStr">
-        <x:is>
-          <x:t>永久+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" s="31" t="inlineStr">
-        <x:is>
-          <x:t>计入羁绊UI和阈值</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="31" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="31" t="inlineStr">
-        <x:is>
-          <x:t>bonus_demon</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="31" t="inlineStr">
-        <x:is>
-          <x:t>魔念入骨</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" s="31" t="inlineStr">
-        <x:is>
-          <x:t>羁绊</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E6" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F6" s="31" t="inlineStr">
-        <x:is>
-          <x:t>魔修激活数+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G6" s="31" t="inlineStr">
-        <x:is>
-          <x:t>永久+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H6" s="31" t="inlineStr">
-        <x:is>
-          <x:t>计入羁绊UI和阈值</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="31" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B7" s="31" t="inlineStr">
-        <x:is>
-          <x:t>bonus_metal</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="31" t="inlineStr">
-        <x:is>
-          <x:t>金炁入怀</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D7" s="31" t="inlineStr">
-        <x:is>
-          <x:t>羁绊</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E7" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F7" s="31" t="inlineStr">
-        <x:is>
-          <x:t>金激活数+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G7" s="31" t="inlineStr">
-        <x:is>
-          <x:t>永久+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H7" s="31" t="inlineStr">
-        <x:is>
-          <x:t>计入羁绊UI和阈值</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="22" customHeight="1">
-      <x:c r="A8" s="31" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B8" s="31" t="inlineStr">
-        <x:is>
-          <x:t>bonus_wood</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="31" t="inlineStr">
-        <x:is>
-          <x:t>木灵垂青</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" s="31" t="inlineStr">
-        <x:is>
-          <x:t>羁绊</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E8" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F8" s="31" t="inlineStr">
-        <x:is>
-          <x:t>木激活数+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G8" s="31" t="inlineStr">
-        <x:is>
-          <x:t>永久+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H8" s="31" t="inlineStr">
-        <x:is>
-          <x:t>计入羁绊UI和阈值</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="22" customHeight="1">
-      <x:c r="A9" s="31" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B9" s="31" t="inlineStr">
-        <x:is>
-          <x:t>bonus_water</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="31" t="inlineStr">
-        <x:is>
-          <x:t>水脉回响</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9" s="31" t="inlineStr">
-        <x:is>
-          <x:t>羁绊</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E9" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F9" s="31" t="inlineStr">
-        <x:is>
-          <x:t>水激活数+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G9" s="31" t="inlineStr">
-        <x:is>
-          <x:t>永久+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H9" s="31" t="inlineStr">
-        <x:is>
-          <x:t>计入羁绊UI和阈值</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="31" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B10" s="31" t="inlineStr">
-        <x:is>
-          <x:t>bonus_fire</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="31" t="inlineStr">
-        <x:is>
-          <x:t>火种跃动</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" s="31" t="inlineStr">
-        <x:is>
-          <x:t>羁绊</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E10" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F10" s="31" t="inlineStr">
-        <x:is>
-          <x:t>火激活数+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G10" s="31" t="inlineStr">
-        <x:is>
-          <x:t>永久+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H10" s="31" t="inlineStr">
-        <x:is>
-          <x:t>计入羁绊UI和阈值</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="22" customHeight="1">
-      <x:c r="A11" s="31" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B11" s="31" t="inlineStr">
-        <x:is>
-          <x:t>bonus_earth</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="31" t="inlineStr">
-        <x:is>
-          <x:t>土德护身</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D11" s="31" t="inlineStr">
-        <x:is>
-          <x:t>羁绊</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E11" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F11" s="31" t="inlineStr">
-        <x:is>
-          <x:t>土激活数+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G11" s="31" t="inlineStr">
-        <x:is>
-          <x:t>永久+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H11" s="31" t="inlineStr">
-        <x:is>
-          <x:t>计入羁绊UI和阈值</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="31" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B12" s="31" t="inlineStr">
-        <x:is>
-          <x:t>bonus_lightning</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="31" t="inlineStr">
-        <x:is>
-          <x:t>雷纹贯体</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D12" s="31" t="inlineStr">
-        <x:is>
-          <x:t>羁绊</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E12" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" s="31" t="inlineStr">
-        <x:is>
-          <x:t>雷激活数+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G12" s="31" t="inlineStr">
-        <x:is>
-          <x:t>永久+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H12" s="31" t="inlineStr">
-        <x:is>
-          <x:t>计入羁绊UI和阈值</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="22" customHeight="1">
-      <x:c r="A13" s="31" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B13" s="31" t="inlineStr">
-        <x:is>
-          <x:t>bonus_poison</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="31" t="inlineStr">
-        <x:is>
-          <x:t>毒脉暗生</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D13" s="31" t="inlineStr">
-        <x:is>
-          <x:t>羁绊</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E13" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" s="31" t="inlineStr">
-        <x:is>
-          <x:t>毒激活数+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G13" s="31" t="inlineStr">
-        <x:is>
-          <x:t>永久+1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H13" s="31" t="inlineStr">
-        <x:is>
-          <x:t>计入羁绊UI和阈值</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="31" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B14" s="31" t="inlineStr">
-        <x:is>
-          <x:t>gain_300_stones</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="31" t="inlineStr">
-        <x:is>
-          <x:t>洞府遗财</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D14" s="31" t="inlineStr">
-        <x:is>
-          <x:t>经济</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E14" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F14" s="31" t="inlineStr">
-        <x:is>
-          <x:t>立即获得300灵石</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G14" s="31" t="inlineStr">
-        <x:is>
-          <x:t>+300灵石</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H14" s="31" t="inlineStr">
-        <x:is>
-          <x:t>选择后立刻到账</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="22" customHeight="1">
-      <x:c r="A15" s="31" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B15" s="31" t="inlineStr">
-        <x:is>
-          <x:t>free_rerolls_3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" s="31" t="inlineStr">
-        <x:is>
-          <x:t>天机自现</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D15" s="31" t="inlineStr">
-        <x:is>
-          <x:t>经济</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E15" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F15" s="31" t="inlineStr">
-        <x:is>
-          <x:t>接下来3次商店刷新免费</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G15" s="31" t="inlineStr">
-        <x:is>
-          <x:t>3次商店</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H15" s="31" t="inlineStr">
-        <x:is>
-          <x:t>每次商店内任意刷新均为0灵石</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="31" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B16" s="31" t="inlineStr">
-        <x:is>
-          <x:t>half_price_1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C16" s="31" t="inlineStr">
-        <x:is>
-          <x:t>仙市折券</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D16" s="31" t="inlineStr">
-        <x:is>
-          <x:t>经济</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E16" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F16" s="31" t="inlineStr">
-        <x:is>
-          <x:t>接下来1次商店购买半价</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G16" s="31" t="inlineStr">
-        <x:is>
-          <x:t>1次商店；价格x0.5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H16" s="31" t="inlineStr">
-        <x:is>
-          <x:t>与天命折扣乘算，向上取整</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="22" customHeight="1">
-      <x:c r="A17" s="31" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B17" s="31" t="inlineStr">
-        <x:is>
-          <x:t>next_one_cost_star3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C17" s="31" t="inlineStr">
-        <x:is>
-          <x:t>凡器淬星</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D17" s="31" t="inlineStr">
-        <x:is>
-          <x:t>随机法宝</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E17" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F17" s="31" t="inlineStr">
-        <x:is>
-          <x:t>下次购买的1费法宝直接升级到3星</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G17" s="31" t="inlineStr">
-        <x:is>
-          <x:t>直到买到凡器后消耗</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H17" s="31" t="inlineStr">
-        <x:is>
-          <x:t>非凡器购买不消耗效果</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="31" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B18" s="31" t="inlineStr">
-        <x:is>
-          <x:t>random_star_up</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C18" s="31" t="inlineStr">
-        <x:is>
-          <x:t>星辉点化</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D18" s="31" t="inlineStr">
-        <x:is>
-          <x:t>随机法宝</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E18" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F18" s="31" t="inlineStr">
-        <x:is>
-          <x:t>随机一个法宝升1星</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G18" s="31" t="inlineStr">
-        <x:is>
-          <x:t>立即；最高3星</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H18" s="31" t="inlineStr">
-        <x:is>
-          <x:t>从出战区和储物袋中随机可升星法宝</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="22" customHeight="1">
-      <x:c r="A19" s="31" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B19" s="31" t="inlineStr">
-        <x:is>
-          <x:t>reroll_higher_tier</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C19" s="31" t="inlineStr">
-        <x:is>
-          <x:t>灵宝换胎</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D19" s="31" t="inlineStr">
-        <x:is>
-          <x:t>随机法宝</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E19" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F19" s="31" t="inlineStr">
-        <x:is>
-          <x:t>场上所有法宝随机变成高一品阶但同一星级的法宝</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G19" s="31" t="inlineStr">
-        <x:is>
-          <x:t>立即；5费不变</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H19" s="31" t="inlineStr">
-        <x:is>
-          <x:t>出战区和储物袋都处理；保持星级</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="31" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B20" s="31" t="inlineStr">
-        <x:is>
-          <x:t>synergy_damage</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C20" s="31" t="inlineStr">
-        <x:is>
-          <x:t>万法归一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D20" s="31" t="inlineStr">
-        <x:is>
-          <x:t>Build强化</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E20" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F20" s="31" t="inlineStr">
-        <x:is>
-          <x:t>每激活一个羁绊，伤害+5%</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G20" s="31" t="inlineStr">
-        <x:is>
-          <x:t>每个已激活羁绊+5%</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H20" s="31" t="inlineStr">
-        <x:is>
-          <x:t>按当前激活羁绊数动态计算</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="22" customHeight="1">
-      <x:c r="A21" s="31" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B21" s="31" t="inlineStr">
-        <x:is>
-          <x:t>revive_once</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C21" s="31" t="inlineStr">
-        <x:is>
-          <x:t>替死符</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D21" s="31" t="inlineStr">
-        <x:is>
-          <x:t>生存</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E21" s="31" t="inlineStr">
-        <x:is>
-          <x:t>击败Boss关后三选一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F21" s="31" t="inlineStr">
-        <x:is>
-          <x:t>死亡后以50%血量复活一次</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G21" s="31" t="inlineStr">
-        <x:is>
-          <x:t>一次；50%最大生命</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H21" s="31" t="inlineStr">
-        <x:is>
-          <x:t>触发后消耗</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
 </file>
--- a/docs/GameBalance.updated.xlsx
+++ b/docs/GameBalance.updated.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rb20be797034c4831"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤害系统" sheetId="2" r:id="Ra57af3dea62943b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="3" r:id="R08349aa6f67d4474"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关卡成长" sheetId="4" r:id="R0abc8e58cec842ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊说明" sheetId="5" r:id="Rfc7bfca95db04669"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="6" r:id="Re0d25b9eb73c4f3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命奇遇效果索引" sheetId="7" r:id="Rec8ae949c3c54cb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R3dcc89cd8789460e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤害系统" sheetId="2" r:id="Rb6504e10203a4f89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="3" r:id="R1485300636e14a35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关卡成长" sheetId="4" r:id="Re85fbe1c264043af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊说明" sheetId="5" r:id="Rc47746995a6e47d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="6" r:id="R1b893292886440ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命奇遇效果索引" sheetId="7" r:id="R654dfea34ee64a47"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -429,7 +429,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B3" s="5" t="n">
-        <x:v>46200.64384505787</x:v>
+        <x:v>46200.783423472225</x:v>
       </x:c>
     </x:row>
     <x:row r="4">

--- a/docs/GameBalance.updated.xlsx
+++ b/docs/GameBalance.updated.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R3dcc89cd8789460e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤害系统" sheetId="2" r:id="Rb6504e10203a4f89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="3" r:id="R1485300636e14a35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关卡成长" sheetId="4" r:id="Re85fbe1c264043af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊说明" sheetId="5" r:id="Rc47746995a6e47d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="6" r:id="R1b893292886440ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命奇遇效果索引" sheetId="7" r:id="R654dfea34ee64a47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R717e6fd974494ac0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤害系统" sheetId="2" r:id="Ra15d56dd3e7a461c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="3" r:id="Rbdaf19d88db34a36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关卡成长" sheetId="4" r:id="R9e871a4486304821"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊说明" sheetId="5" r:id="R0587959917244df5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="6" r:id="R4d826c94d6e549b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命奇遇效果索引" sheetId="7" r:id="R99869510173545a3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -429,7 +429,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B3" s="5" t="n">
-        <x:v>46200.783423472225</x:v>
+        <x:v>46200.794970856485</x:v>
       </x:c>
     </x:row>
     <x:row r="4">

--- a/docs/GameBalance.updated.xlsx
+++ b/docs/GameBalance.updated.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R717e6fd974494ac0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤害系统" sheetId="2" r:id="Ra15d56dd3e7a461c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="3" r:id="Rbdaf19d88db34a36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关卡成长" sheetId="4" r:id="R9e871a4486304821"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊说明" sheetId="5" r:id="R0587959917244df5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="6" r:id="R4d826c94d6e549b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命奇遇效果索引" sheetId="7" r:id="R99869510173545a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rca3c3ee4e95e45dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤害系统" sheetId="2" r:id="Ra296b876d53c4ffc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="3" r:id="R41522c7cd01b4a60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关卡成长" sheetId="4" r:id="Rb6b758891d2c4f90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊说明" sheetId="5" r:id="R04001078a4a040e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="6" r:id="Rfd9b63875d5b47c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命奇遇效果索引" sheetId="7" r:id="R23d935e5e09f4ca4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -429,7 +429,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B3" s="5" t="n">
-        <x:v>46200.794970856485</x:v>
+        <x:v>46200.80714304398</x:v>
       </x:c>
     </x:row>
     <x:row r="4">

--- a/docs/GameBalance.updated.xlsx
+++ b/docs/GameBalance.updated.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rca3c3ee4e95e45dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤害系统" sheetId="2" r:id="Ra296b876d53c4ffc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="3" r:id="R41522c7cd01b4a60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关卡成长" sheetId="4" r:id="Rb6b758891d2c4f90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊说明" sheetId="5" r:id="R04001078a4a040e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="6" r:id="Rfd9b63875d5b47c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命奇遇效果索引" sheetId="7" r:id="R23d935e5e09f4ca4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R8e429f8be9da4f10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤害系统" sheetId="2" r:id="R0539c96e840f44ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="3" r:id="R64e1c56f71c94c8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关卡成长" sheetId="4" r:id="R6ca8bd4dd9cc4eec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊说明" sheetId="5" r:id="R70b5bb000b834153"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="6" r:id="R0d58f630cf0a4c0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命奇遇效果索引" sheetId="7" r:id="R24dcbd1739aa4d68"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -429,7 +429,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B3" s="5" t="n">
-        <x:v>46200.80714304398</x:v>
+        <x:v>46200.98272409722</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1991,7 +1991,7 @@
         <x:v>法宝</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>特殊效果类型：damage/slow/attack_speed/heal/shield/damage_reduction/counter_damage/avatar_slam。</x:v>
+        <x:v>特殊效果类型：damage/slow/attack_speed/heal/shield/damage_reduction/avatar_slam。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="34.5" hidden="0" customHeight="1">
